--- a/App_Data/templates/檢驗template.xlsx
+++ b/App_Data/templates/檢驗template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
+<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr dateCompatibility="0" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F570F2C9-F846-44C2-8584-648EF4D7CA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{36E585E1-2044-4560-9E5A-0DBC6DA7C72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{17681C7F-D386-4A82-BD7B-22ABDFEC6765}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="142">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="385" uniqueCount="142">
   <si>
     <t>來源單據</t>
   </si>
@@ -513,7 +513,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1641,7 +1641,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1690,7 +1690,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2006,7 +2006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB4B9AD-CF51-4547-B104-ED6B3BAA2CA7}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB4B9AD-CF51-4547-B104-ED6B3BAA2CA7}">
   <sheetPr codeName="工作表1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2535,7 +2535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E234548-FB06-40AB-A556-44D02F0246AB}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E234548-FB06-40AB-A556-44D02F0246AB}">
   <sheetPr codeName="工作表2"/>
   <dimension ref="A1:AE16"/>
   <sheetFormatPr defaultColWidth="6.77734375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -3179,7 +3179,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF310D-CF1D-47A0-8C40-55D9D039B5E9}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF310D-CF1D-47A0-8C40-55D9D039B5E9}">
   <sheetPr codeName="工作表3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3782,7 +3782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09578F8-2C20-4D38-BBDA-E3376BD7EF4B}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09578F8-2C20-4D38-BBDA-E3376BD7EF4B}">
   <dimension ref="A1:U10"/>
   <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>

--- a/App_Data/templates/檢驗template.xlsx
+++ b/App_Data/templates/檢驗template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr dateCompatibility="0" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Yoruru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{36E585E1-2044-4560-9E5A-0DBC6DA7C72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85839C02-43B5-4AFF-93DC-4412074A350A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{17681C7F-D386-4A82-BD7B-22ABDFEC6765}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17681C7F-D386-4A82-BD7B-22ABDFEC6765}"/>
   </bookViews>
   <sheets>
     <sheet name="templete" sheetId="3" r:id="rId1"/>
@@ -22,26 +22,12 @@
     <definedName name="LOOP_ROW" localSheetId="0">templete!$W$15</definedName>
     <definedName name="LOOP_ROW">shiisa!$W$17</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="385" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="142">
   <si>
     <t>來源單據</t>
   </si>
@@ -513,7 +499,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -918,15 +904,15 @@
   </fills>
   <borders count="27">
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thick">
         <color theme="4"/>
@@ -934,8 +920,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thick">
         <color theme="4" tint="0.499984740745262"/>
@@ -943,8 +929,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.39997558519241921"/>
@@ -952,12 +938,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
-      </start>
-      <end style="thin">
+      </left>
+      <right style="thin">
         <color rgb="FF7F7F7F"/>
-      </end>
+      </right>
       <top style="thin">
         <color rgb="FF7F7F7F"/>
       </top>
@@ -967,12 +953,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
-      </start>
-      <end style="thin">
+      </left>
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
-      </end>
+      </right>
       <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -982,8 +968,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -991,12 +977,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="double">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
-      </start>
-      <end style="double">
+      </left>
+      <right style="double">
         <color rgb="FF3F3F3F"/>
-      </end>
+      </right>
       <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -1006,12 +992,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
-      </start>
-      <end style="thin">
+      </left>
+      <right style="thin">
         <color rgb="FFB2B2B2"/>
-      </end>
+      </right>
       <top style="thin">
         <color rgb="FFB2B2B2"/>
       </top>
@@ -1021,8 +1007,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1032,12 +1018,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1047,10 +1033,10 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1060,8 +1046,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1071,10 +1057,10 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1084,12 +1070,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1099,12 +1085,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1112,10 +1098,10 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1125,10 +1111,10 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1138,12 +1124,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="medium">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1153,12 +1139,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1168,12 +1154,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="thin">
-        <color indexed="64"/>
-      </start>
-      <end style="medium">
-        <color indexed="64"/>
-      </end>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1183,12 +1169,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="medium">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1198,10 +1184,10 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end style="medium">
-        <color indexed="64"/>
-      </end>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1211,12 +1197,12 @@
       <diagonal/>
     </border>
     <border>
-      <start style="medium">
-        <color indexed="64"/>
-      </start>
-      <end style="thin">
-        <color indexed="64"/>
-      </end>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1226,10 +1212,10 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end style="medium">
-        <color indexed="64"/>
-      </end>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1239,8 +1225,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1248,8 +1234,8 @@
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1460,6 +1446,51 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1469,53 +1500,26 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1526,32 +1530,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="42" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="42" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="42" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1613,7 +1599,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>16</xdr:col>
@@ -1641,7 +1627,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1662,7 +1648,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>16</xdr:col>
@@ -1690,7 +1676,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1711,7 +1697,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1864,25 +1850,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110%"/>
-                <a:satMod val="105%"/>
-                <a:tint val="67%"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="103%"/>
-                <a:tint val="73%"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="109%"/>
-                <a:tint val="81%"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1890,25 +1876,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103%"/>
-                <a:lumMod val="102%"/>
-                <a:tint val="94%"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110%"/>
-                <a:lumMod val="100%"/>
-                <a:shade val="100%"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99%"/>
-                <a:satMod val="120%"/>
-                <a:shade val="78%"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1921,21 +1907,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1949,7 +1935,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63%"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -1961,32 +1947,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95%"/>
-            <a:satMod val="170%"/>
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93%"/>
-                <a:satMod val="150%"/>
-                <a:shade val="98%"/>
-                <a:lumMod val="102%"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="98%"/>
-                <a:satMod val="130%"/>
-                <a:shade val="90%"/>
-                <a:lumMod val="103%"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63%"/>
-                <a:satMod val="120%"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2006,326 +1992,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB4B9AD-CF51-4547-B104-ED6B3BAA2CA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB4B9AD-CF51-4547-B104-ED6B3BAA2CA7}">
   <sheetPr codeName="工作表1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X12"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.5546875" style="12"/>
+    <col min="1" max="16384" width="8.5" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:24" ht="80.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="30" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="29" t="s">
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="25"/>
+      <c r="K2" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="29" t="s">
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="29"/>
-      <c r="P2" s="41" t="s">
+      <c r="O2" s="25"/>
+      <c r="P2" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+    </row>
+    <row r="3" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="39" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="K3" s="30" t="s">
+      <c r="J3" s="25"/>
+      <c r="K3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="29" t="s">
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="29"/>
-      <c r="P3" s="30" t="s">
+      <c r="O3" s="25"/>
+      <c r="P3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="29" t="s">
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="30" t="s">
+      <c r="T3" s="25"/>
+      <c r="U3" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+    </row>
+    <row r="4" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="29" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="29"/>
-      <c r="P4" s="30" t="s">
+      <c r="O4" s="25"/>
+      <c r="P4" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-    </row>
-    <row r="5" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+    </row>
+    <row r="5" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-    </row>
-    <row r="6" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+    </row>
+    <row r="6" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="29" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="30" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="29" t="s">
+      <c r="H6" s="24"/>
+      <c r="I6" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30" t="s">
+      <c r="J6" s="25"/>
+      <c r="K6" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="29" t="s">
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="37" t="s">
+      <c r="T6" s="25"/>
+      <c r="U6" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-    </row>
-    <row r="7" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+    </row>
+    <row r="7" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-    </row>
-    <row r="8" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+    </row>
+    <row r="8" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="27"/>
-    </row>
-    <row r="9" spans="1:24" s="20" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="36"/>
+    </row>
+    <row r="9" spans="1:24" s="20" customFormat="1" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-    </row>
-    <row r="10" spans="1:24" s="15" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+    </row>
+    <row r="10" spans="1:24" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="14" t="s">
         <v>31</v>
       </c>
@@ -2338,10 +2324,10 @@
       <c r="G10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="35"/>
+      <c r="I10" s="29"/>
       <c r="J10" s="14">
         <v>1</v>
       </c>
@@ -2381,19 +2367,19 @@
       <c r="V10" s="14">
         <v>13</v>
       </c>
-      <c r="W10" s="35" t="s">
+      <c r="W10" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="X10" s="36"/>
-    </row>
-    <row r="11" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X10" s="30"/>
+    </row>
+    <row r="11" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="11" t="s">
         <v>135</v>
       </c>
@@ -2406,10 +2392,10 @@
       <c r="G11" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="36"/>
       <c r="J11" s="22" t="s">
         <v>121</v>
       </c>
@@ -2449,21 +2435,21 @@
       <c r="V11" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="W11" s="26" t="s">
+      <c r="W11" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="X11" s="28"/>
-    </row>
-    <row r="12" spans="1:24" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X11" s="41"/>
+    </row>
+    <row r="12" spans="1:24" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
@@ -2477,31 +2463,19 @@
       <c r="T12" s="18"/>
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="25"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="Q1:X1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:X2"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="C8:X8"/>
+    <mergeCell ref="B9:X9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="W11:X11"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="W10:X10"/>
@@ -2518,14 +2492,26 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:X7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:X8"/>
-    <mergeCell ref="B9:X9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="Q1:X1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:X2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2535,33 +2521,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E234548-FB06-40AB-A556-44D02F0246AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E234548-FB06-40AB-A556-44D02F0246AB}">
   <sheetPr codeName="工作表2"/>
   <dimension ref="A1:AE16"/>
-  <sheetFormatPr defaultColWidth="6.77734375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="6.44140625" customWidth="1"/>
+    <col min="1" max="3" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:31" ht="65.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
       <c r="Q1" s="10"/>
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
@@ -2572,52 +2558,52 @@
       <c r="X1" s="10"/>
       <c r="Y1" s="10"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42">
+      <c r="K2" s="48"/>
+      <c r="L2" s="48">
         <v>40</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42" t="s">
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="43"/>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="49"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="48" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="50"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
@@ -2650,11 +2636,11 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="46"/>
+      <c r="B4" s="47"/>
       <c r="C4" s="5" t="s">
         <v>48</v>
       </c>
@@ -2687,11 +2673,11 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="46"/>
+      <c r="B5" s="47"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
         <v>13</v>
@@ -2718,11 +2704,11 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="46"/>
+      <c r="B6" s="47"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>20</v>
@@ -2753,19 +2739,19 @@
         <v>19</v>
       </c>
       <c r="T6" s="1"/>
-      <c r="U6" s="2" t="d">
-        <v>2026-07-03</v>
+      <c r="U6" s="2">
+        <v>46206</v>
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="46"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -2792,11 +2778,11 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="46"/>
+      <c r="B8" s="47"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -2823,7 +2809,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2850,7 +2836,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:31" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -2877,7 +2863,7 @@
       <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2879,8 @@
         <v>26</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="7" t="d">
-        <v>2026-07-03T13:33:58.99999991990625900</v>
+      <c r="J11" s="7">
+        <v>46206.565266203703</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="6"/>
@@ -2916,7 +2902,7 @@
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -2988,7 +2974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -3035,7 +3021,7 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -3082,7 +3068,7 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3129,7 +3115,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -3158,6 +3144,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C2:I2"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A7:B7"/>
@@ -3166,12 +3158,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C2:I2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3179,324 +3165,324 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF310D-CF1D-47A0-8C40-55D9D039B5E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF310D-CF1D-47A0-8C40-55D9D039B5E9}">
   <sheetPr codeName="工作表3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X14"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.5546875" style="12"/>
+    <col min="1" max="16384" width="8.5" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:24" ht="80.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="29" t="s">
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="25"/>
+      <c r="K2" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="29" t="s">
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="29"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="O2" s="25"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+    </row>
+    <row r="3" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="39" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="K3" s="30" t="s">
+      <c r="J3" s="25"/>
+      <c r="K3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="29" t="s">
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="29"/>
-      <c r="P3" s="30" t="s">
+      <c r="O3" s="25"/>
+      <c r="P3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="29" t="s">
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="30" t="s">
+      <c r="T3" s="25"/>
+      <c r="U3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+    </row>
+    <row r="4" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="29" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="29"/>
-      <c r="P4" s="30" t="s">
+      <c r="O4" s="25"/>
+      <c r="P4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-    </row>
-    <row r="5" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+    </row>
+    <row r="5" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-    </row>
-    <row r="6" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+    </row>
+    <row r="6" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30">
+      <c r="B6" s="25"/>
+      <c r="C6" s="24">
         <v>20</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="29" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="30" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="29" t="s">
+      <c r="H6" s="24"/>
+      <c r="I6" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30" t="s">
+      <c r="J6" s="25"/>
+      <c r="K6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="29" t="s">
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="37" t="d">
-        <v>2026-07-03</v>
-      </c>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-    </row>
-    <row r="7" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="T6" s="25"/>
+      <c r="U6" s="31">
+        <v>46206</v>
+      </c>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+    </row>
+    <row r="7" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-    </row>
-    <row r="8" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+    </row>
+    <row r="8" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="27"/>
-    </row>
-    <row r="9" spans="1:24" s="20" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="36"/>
+    </row>
+    <row r="9" spans="1:24" s="20" customFormat="1" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-    </row>
-    <row r="10" spans="1:24" s="15" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+    </row>
+    <row r="10" spans="1:24" s="15" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="14" t="s">
         <v>31</v>
       </c>
@@ -3509,10 +3495,10 @@
       <c r="G10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="35"/>
+      <c r="I10" s="29"/>
       <c r="J10" s="14">
         <v>1</v>
       </c>
@@ -3552,19 +3538,19 @@
       <c r="V10" s="14">
         <v>13</v>
       </c>
-      <c r="W10" s="35" t="s">
+      <c r="W10" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="X10" s="36"/>
-    </row>
-    <row r="11" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X10" s="30"/>
+    </row>
+    <row r="11" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>1</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="11">
         <v>1</v>
       </c>
@@ -3577,10 +3563,10 @@
       <c r="G11" s="11">
         <v>0</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="36"/>
       <c r="J11" s="11" t="s">
         <v>39</v>
       </c>
@@ -3598,19 +3584,19 @@
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
-      <c r="W11" s="26" t="s">
+      <c r="W11" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="X11" s="28"/>
-    </row>
-    <row r="12" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X11" s="41"/>
+    </row>
+    <row r="12" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>2</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="27"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="11">
         <v>2</v>
       </c>
@@ -3623,10 +3609,10 @@
       <c r="G12" s="11">
         <v>0</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="27"/>
+      <c r="I12" s="36"/>
       <c r="J12" s="11" t="s">
         <v>39</v>
       </c>
@@ -3644,19 +3630,19 @@
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
-      <c r="W12" s="26" t="s">
+      <c r="W12" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="X12" s="28"/>
-    </row>
-    <row r="13" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X12" s="41"/>
+    </row>
+    <row r="13" spans="1:24" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>3</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="11">
         <v>3</v>
       </c>
@@ -3669,10 +3655,10 @@
       <c r="G13" s="11">
         <v>0</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="27"/>
+      <c r="I13" s="36"/>
       <c r="J13" s="11" t="s">
         <v>39</v>
       </c>
@@ -3690,21 +3676,21 @@
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
-      <c r="W13" s="26" t="s">
+      <c r="W13" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="X13" s="28"/>
-    </row>
-    <row r="14" spans="1:24" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X13" s="41"/>
+    </row>
+    <row r="14" spans="1:24" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="24"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="39"/>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
@@ -3718,29 +3704,27 @@
       <c r="T14" s="18"/>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="25"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:X2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="Q1:X1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="C5:X5"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="C7:X7"/>
+    <mergeCell ref="C8:X8"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="W10:X10"/>
@@ -3757,22 +3741,24 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="C5:X5"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="C7:X7"/>
-    <mergeCell ref="C8:X8"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="Q1:X1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:X2"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3782,101 +3768,101 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09578F8-2C20-4D38-BBDA-E3376BD7EF4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09578F8-2C20-4D38-BBDA-E3376BD7EF4B}">
   <dimension ref="A1:U10"/>
-  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="8" max="20" width="6.6640625" customWidth="1"/>
+    <col min="3" max="6" width="8.875" customWidth="1"/>
+    <col min="8" max="20" width="6.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="L1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="M1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="O1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="R1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="T1" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="U1" s="53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="S1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="T1" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="51" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
         <v>69</v>
       </c>
       <c r="B2" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="51" t="s">
+      <c r="D2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="53" t="s">
         <v>68</v>
       </c>
       <c r="H2" s="52" t="s">
@@ -3885,19 +3871,19 @@
       <c r="I2" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="51" t="s">
+      <c r="K2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="53" t="s">
         <v>68</v>
       </c>
       <c r="O2" s="52" t="s">
@@ -3906,42 +3892,42 @@
       <c r="P2" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="R2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T2" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U2" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="51" t="s">
+      <c r="D3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="53" t="s">
         <v>68</v>
       </c>
       <c r="H3" s="52" t="s">
@@ -3950,19 +3936,19 @@
       <c r="I3" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="51" t="s">
+      <c r="K3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" s="53" t="s">
         <v>68</v>
       </c>
       <c r="O3" s="52" t="s">
@@ -3971,42 +3957,42 @@
       <c r="P3" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="R3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U3" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T3" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U3" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="51" t="s">
+      <c r="D4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="53" t="s">
         <v>68</v>
       </c>
       <c r="H4" s="52" t="s">
@@ -4015,19 +4001,19 @@
       <c r="I4" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N4" s="51" t="s">
+      <c r="K4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="53" t="s">
         <v>68</v>
       </c>
       <c r="O4" s="52" t="s">
@@ -4036,107 +4022,107 @@
       <c r="P4" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="Q4" s="51" t="s">
+      <c r="Q4" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="R4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U4" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T4" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="P5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="R5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U5" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T5" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U5" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="51" t="s">
+      <c r="D6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="53" t="s">
         <v>68</v>
       </c>
       <c r="H6" s="52" t="s">
@@ -4145,19 +4131,19 @@
       <c r="I6" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="51" t="s">
+      <c r="J6" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N6" s="51" t="s">
+      <c r="K6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="53" t="s">
         <v>68</v>
       </c>
       <c r="O6" s="52" t="s">
@@ -4166,42 +4152,42 @@
       <c r="P6" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="Q6" s="51" t="s">
+      <c r="Q6" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="R6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U6" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T6" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U6" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="51" t="s">
+      <c r="D7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="53" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="52" t="s">
@@ -4210,19 +4196,19 @@
       <c r="I7" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="51" t="s">
+      <c r="J7" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="51" t="s">
+      <c r="K7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7" s="53" t="s">
         <v>68</v>
       </c>
       <c r="O7" s="52" t="s">
@@ -4231,88 +4217,88 @@
       <c r="P7" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="Q7" s="51" t="s">
+      <c r="Q7" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="R7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="P8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="R8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="S8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="T8" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" s="51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T7" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="R8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="S8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="T8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="U8" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>88</v>
       </c>
@@ -4377,7 +4363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>102</v>
       </c>
@@ -4444,13 +4430,21 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:U6"/>
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:G3"/>
@@ -4463,21 +4457,13 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:U5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:U6"/>
-    <mergeCell ref="A8:U8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="Q7:U7"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/App_Data/templates/檢驗template.xlsx
+++ b/App_Data/templates/檢驗template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F586C6E-221C-4060-85BC-F480897098B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3410DC5C-F253-4512-B2D0-771D80713B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{17681C7F-D386-4A82-BD7B-22ABDFEC6765}"/>
   </bookViews>
@@ -1877,6 +1877,24 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1889,12 +1907,6 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1904,17 +1916,53 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1930,190 +1978,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
@@ -2122,6 +1986,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2618,306 +2618,306 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="32" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
     </row>
     <row r="2" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="31" t="s">
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="39" t="s">
+      <c r="J2" s="29"/>
+      <c r="K2" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="31" t="s">
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="31"/>
-      <c r="P2" s="39" t="s">
+      <c r="O2" s="29"/>
+      <c r="P2" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
     </row>
     <row r="3" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="37" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="31" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32" t="s">
+      <c r="J3" s="29"/>
+      <c r="K3" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="31" t="s">
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="32" t="s">
+      <c r="O3" s="29"/>
+      <c r="P3" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="31" t="s">
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="31"/>
-      <c r="U3" s="32" t="s">
+      <c r="T3" s="29"/>
+      <c r="U3" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
     </row>
     <row r="4" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="36" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="31" t="s">
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="31"/>
-      <c r="P4" s="32" t="s">
+      <c r="O4" s="29"/>
+      <c r="P4" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
     </row>
     <row r="5" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
     </row>
     <row r="6" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="28"/>
+      <c r="E6" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32" t="s">
+      <c r="F6" s="29"/>
+      <c r="G6" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="31" t="s">
+      <c r="H6" s="28"/>
+      <c r="I6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="31"/>
-      <c r="K6" s="32" t="s">
+      <c r="J6" s="29"/>
+      <c r="K6" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="31" t="s">
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="31"/>
-      <c r="U6" s="33" t="s">
+      <c r="T6" s="29"/>
+      <c r="U6" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="37"/>
     </row>
     <row r="7" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="32"/>
-      <c r="U7" s="32"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="32"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
     </row>
     <row r="8" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="29"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="35"/>
     </row>
     <row r="9" spans="1:24" s="7" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
     </row>
     <row r="10" spans="1:24" s="3" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3026,26 +3026,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="Q1:X1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:X2"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:R3"/>
     <mergeCell ref="C8:X8"/>
     <mergeCell ref="B9:X9"/>
     <mergeCell ref="A5:B5"/>
@@ -3061,6 +3041,26 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:X7"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="Q1:X1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:X2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3075,51 +3075,51 @@
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="52" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="49"/>
-      <c r="K1" s="53" t="s">
+      <c r="J1" s="44"/>
+      <c r="K1" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="52" t="s">
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="56"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="45" t="s">
+      <c r="T1" s="51"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="W1" s="46"/>
-      <c r="X1" s="47"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="42"/>
     </row>
     <row r="2" spans="1:24" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="54"/>
       <c r="D2" s="10" t="s">
         <v>23</v>
       </c>
@@ -3132,10 +3132,10 @@
       <c r="G2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="42"/>
+      <c r="I2" s="54"/>
       <c r="J2" s="10">
         <v>1</v>
       </c>
@@ -3175,19 +3175,19 @@
       <c r="V2" s="10">
         <v>13</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="W2" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="X2" s="43"/>
+      <c r="X2" s="55"/>
     </row>
     <row r="3" spans="1:24" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="32"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="1" t="s">
         <v>71</v>
       </c>
@@ -3200,10 +3200,10 @@
       <c r="G3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="32"/>
+      <c r="I3" s="28"/>
       <c r="J3" s="8" t="s">
         <v>57</v>
       </c>
@@ -3243,21 +3243,21 @@
       <c r="V3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W3" s="32" t="s">
+      <c r="W3" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="X3" s="44"/>
+      <c r="X3" s="56"/>
     </row>
     <row r="4" spans="1:24" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -3271,8 +3271,8 @@
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="41"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="53"/>
     </row>
     <row r="5" spans="1:24" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -3328,12 +3328,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="S1:U1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="W4:X4"/>
@@ -3343,6 +3337,12 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="W3:X3"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="S1:U1"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3365,25 +3365,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="T1" s="11"/>
@@ -3399,317 +3399,317 @@
       <c r="AD1" s="11"/>
     </row>
     <row r="2" spans="1:30" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="92"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
-      <c r="T2" s="92"/>
-      <c r="U2" s="92"/>
-      <c r="V2" s="92"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="92"/>
-      <c r="Y2" s="92"/>
-      <c r="Z2" s="92"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="58"/>
+      <c r="Z2" s="58"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="11"/>
       <c r="AD2" s="11"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="88" t="s">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="93" t="s">
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="90"/>
-      <c r="M3" s="93" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="93" t="s">
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="90"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
-      <c r="AA3" s="89"/>
-      <c r="AB3" s="89"/>
-      <c r="AC3" s="90"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="61"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="62"/>
+      <c r="AB3" s="62"/>
+      <c r="AC3" s="60"/>
       <c r="AD3" s="11"/>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="88" t="s">
+      <c r="B4" s="65"/>
+      <c r="C4" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="86" t="s">
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="74"/>
-      <c r="M4" s="85" t="s">
+      <c r="L4" s="65"/>
+      <c r="M4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="83" t="s">
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="85" t="s">
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="77"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="83" t="s">
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="85" t="s">
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="AC4" s="74"/>
+      <c r="AC4" s="65"/>
       <c r="AD4" s="11"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="85" t="s">
+      <c r="B5" s="64"/>
+      <c r="C5" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="83" t="s">
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="77"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="84" t="s">
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
-      <c r="W5" s="77"/>
-      <c r="X5" s="77"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="77"/>
-      <c r="AA5" s="77"/>
-      <c r="AB5" s="77"/>
-      <c r="AC5" s="74"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="64"/>
+      <c r="T5" s="64"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="64"/>
+      <c r="AA5" s="64"/>
+      <c r="AB5" s="64"/>
+      <c r="AC5" s="65"/>
       <c r="AD5" s="11"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="84" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
-      <c r="V6" s="77"/>
-      <c r="W6" s="77"/>
-      <c r="X6" s="77"/>
-      <c r="Y6" s="77"/>
-      <c r="Z6" s="77"/>
-      <c r="AA6" s="77"/>
-      <c r="AB6" s="77"/>
-      <c r="AC6" s="74"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64"/>
+      <c r="AA6" s="64"/>
+      <c r="AB6" s="64"/>
+      <c r="AC6" s="65"/>
       <c r="AD6" s="11"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="85" t="s">
+      <c r="B7" s="65"/>
+      <c r="C7" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="83" t="s">
+      <c r="D7" s="64"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="74"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="86" t="s">
+      <c r="G7" s="65"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="77"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="85" t="s">
+      <c r="L7" s="64"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="O7" s="77"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="83" t="s">
+      <c r="O7" s="64"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="85" t="s">
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="65"/>
+      <c r="U7" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="77"/>
-      <c r="Y7" s="77"/>
-      <c r="Z7" s="77"/>
-      <c r="AA7" s="77"/>
-      <c r="AB7" s="77"/>
-      <c r="AC7" s="74"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="64"/>
+      <c r="AB7" s="64"/>
+      <c r="AC7" s="65"/>
       <c r="AD7" s="11"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="74"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="77"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="77"/>
-      <c r="V8" s="77"/>
-      <c r="W8" s="77"/>
-      <c r="X8" s="77"/>
-      <c r="Y8" s="77"/>
-      <c r="Z8" s="77"/>
-      <c r="AA8" s="77"/>
-      <c r="AB8" s="77"/>
-      <c r="AC8" s="74"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="64"/>
+      <c r="AA8" s="64"/>
+      <c r="AB8" s="64"/>
+      <c r="AC8" s="65"/>
       <c r="AD8" s="11"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="74"/>
-      <c r="C9" s="82" t="s">
+      <c r="B9" s="65"/>
+      <c r="C9" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="77"/>
-      <c r="P9" s="77"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="77"/>
-      <c r="S9" s="77"/>
-      <c r="T9" s="77"/>
-      <c r="U9" s="77"/>
-      <c r="V9" s="77"/>
-      <c r="W9" s="77"/>
-      <c r="X9" s="77"/>
-      <c r="Y9" s="77"/>
-      <c r="Z9" s="77"/>
-      <c r="AA9" s="77"/>
-      <c r="AB9" s="77"/>
-      <c r="AC9" s="74"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="64"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="64"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="64"/>
+      <c r="AC9" s="65"/>
       <c r="AD9" s="11"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
@@ -3777,75 +3777,75 @@
       <c r="AD11" s="11"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67" t="s">
+      <c r="B12" s="74"/>
+      <c r="C12" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="69" t="s">
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="66"/>
-      <c r="M12" s="70" t="s">
+      <c r="L12" s="74"/>
+      <c r="M12" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="68"/>
-      <c r="O12" s="68"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="69" t="s">
+      <c r="N12" s="76"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="68"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="68"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="67" t="s">
+      <c r="R12" s="76"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="76"/>
+      <c r="U12" s="74"/>
+      <c r="V12" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="68"/>
-      <c r="X12" s="68"/>
-      <c r="Y12" s="68"/>
-      <c r="Z12" s="68"/>
-      <c r="AA12" s="68"/>
-      <c r="AB12" s="68"/>
-      <c r="AC12" s="71"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="76"/>
+      <c r="Z12" s="76"/>
+      <c r="AA12" s="76"/>
+      <c r="AB12" s="76"/>
+      <c r="AC12" s="79"/>
       <c r="AD12" s="11"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="81"/>
       <c r="D13" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="64" t="s">
+      <c r="E13" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="58"/>
-      <c r="G13" s="64" t="s">
+      <c r="F13" s="81"/>
+      <c r="G13" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="58"/>
+      <c r="H13" s="81"/>
       <c r="I13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="64" t="s">
+      <c r="J13" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="58"/>
+      <c r="K13" s="81"/>
       <c r="L13" s="16">
         <v>1</v>
       </c>
@@ -3861,14 +3861,14 @@
       <c r="P13" s="16">
         <v>5</v>
       </c>
-      <c r="Q13" s="63">
+      <c r="Q13" s="80">
         <v>6</v>
       </c>
-      <c r="R13" s="58"/>
-      <c r="S13" s="63">
+      <c r="R13" s="81"/>
+      <c r="S13" s="80">
         <v>7</v>
       </c>
-      <c r="T13" s="58"/>
+      <c r="T13" s="81"/>
       <c r="U13" s="16">
         <v>8</v>
       </c>
@@ -3878,14 +3878,14 @@
       <c r="W13" s="16">
         <v>10</v>
       </c>
-      <c r="X13" s="63">
+      <c r="X13" s="80">
         <v>11</v>
       </c>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="63">
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="80">
         <v>12</v>
       </c>
-      <c r="AA13" s="58"/>
+      <c r="AA13" s="81"/>
       <c r="AB13" s="16">
         <v>13</v>
       </c>
@@ -3898,28 +3898,28 @@
       <c r="A14" s="18">
         <v>3</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="81"/>
       <c r="D14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="57" t="s">
+      <c r="F14" s="81"/>
+      <c r="G14" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="81"/>
       <c r="I14" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="J14" s="57" t="s">
+      <c r="J14" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="58"/>
+      <c r="K14" s="81"/>
       <c r="L14" s="20" t="s">
         <v>56</v>
       </c>
@@ -3935,17 +3935,17 @@
       <c r="P14" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="57"/>
-      <c r="T14" s="58"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="81"/>
       <c r="U14" s="20"/>
       <c r="V14" s="20"/>
       <c r="W14" s="20"/>
-      <c r="X14" s="57"/>
-      <c r="Y14" s="58"/>
-      <c r="Z14" s="57"/>
-      <c r="AA14" s="58"/>
+      <c r="X14" s="83"/>
+      <c r="Y14" s="81"/>
+      <c r="Z14" s="83"/>
+      <c r="AA14" s="81"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="21" t="s">
         <v>20</v>
@@ -3954,32 +3954,32 @@
     </row>
     <row r="15" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="22"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="60"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="60"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="86"/>
       <c r="I15" s="24"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="60"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="86"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="61"/>
-      <c r="T15" s="60"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="86"/>
+      <c r="S15" s="85"/>
+      <c r="T15" s="86"/>
       <c r="U15" s="24"/>
       <c r="V15" s="24"/>
       <c r="W15" s="24"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="61"/>
-      <c r="AA15" s="60"/>
+      <c r="X15" s="85"/>
+      <c r="Y15" s="86"/>
+      <c r="Z15" s="85"/>
+      <c r="AA15" s="86"/>
       <c r="AB15" s="24"/>
       <c r="AC15" s="25"/>
       <c r="AD15" s="11"/>
@@ -4017,75 +4017,75 @@
       <c r="AD16" s="11"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="67" t="s">
+      <c r="B17" s="74"/>
+      <c r="C17" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="69" t="s">
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="66"/>
-      <c r="M17" s="70" t="s">
+      <c r="L17" s="74"/>
+      <c r="M17" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="N17" s="68"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="69" t="s">
+      <c r="N17" s="76"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="66"/>
-      <c r="V17" s="67" t="s">
+      <c r="R17" s="76"/>
+      <c r="S17" s="76"/>
+      <c r="T17" s="76"/>
+      <c r="U17" s="74"/>
+      <c r="V17" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="W17" s="68"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="68"/>
-      <c r="AA17" s="68"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="71"/>
+      <c r="W17" s="76"/>
+      <c r="X17" s="76"/>
+      <c r="Y17" s="76"/>
+      <c r="Z17" s="76"/>
+      <c r="AA17" s="76"/>
+      <c r="AB17" s="76"/>
+      <c r="AC17" s="79"/>
       <c r="AD17" s="11"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="81"/>
       <c r="D18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="64" t="s">
+      <c r="E18" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="58"/>
-      <c r="G18" s="64" t="s">
+      <c r="F18" s="81"/>
+      <c r="G18" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="58"/>
+      <c r="H18" s="81"/>
       <c r="I18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="64" t="s">
+      <c r="J18" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="58"/>
+      <c r="K18" s="81"/>
       <c r="L18" s="16">
         <v>1</v>
       </c>
@@ -4101,14 +4101,14 @@
       <c r="P18" s="16">
         <v>5</v>
       </c>
-      <c r="Q18" s="63">
+      <c r="Q18" s="80">
         <v>6</v>
       </c>
-      <c r="R18" s="58"/>
-      <c r="S18" s="63">
+      <c r="R18" s="81"/>
+      <c r="S18" s="80">
         <v>7</v>
       </c>
-      <c r="T18" s="58"/>
+      <c r="T18" s="81"/>
       <c r="U18" s="16">
         <v>8</v>
       </c>
@@ -4118,14 +4118,14 @@
       <c r="W18" s="16">
         <v>10</v>
       </c>
-      <c r="X18" s="63">
+      <c r="X18" s="80">
         <v>11</v>
       </c>
-      <c r="Y18" s="58"/>
-      <c r="Z18" s="63">
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="80">
         <v>12</v>
       </c>
-      <c r="AA18" s="58"/>
+      <c r="AA18" s="81"/>
       <c r="AB18" s="16">
         <v>13</v>
       </c>
@@ -4138,28 +4138,28 @@
       <c r="A19" s="18">
         <v>1</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="58"/>
+      <c r="C19" s="81"/>
       <c r="D19" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="57" t="s">
+      <c r="E19" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="58"/>
-      <c r="G19" s="57" t="s">
+      <c r="F19" s="81"/>
+      <c r="G19" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="58"/>
+      <c r="H19" s="81"/>
       <c r="I19" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J19" s="57" t="s">
+      <c r="J19" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K19" s="58"/>
+      <c r="K19" s="81"/>
       <c r="L19" s="20" t="s">
         <v>103</v>
       </c>
@@ -4175,17 +4175,17 @@
       <c r="P19" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="58"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="83"/>
+      <c r="T19" s="81"/>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="58"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="58"/>
+      <c r="X19" s="83"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="83"/>
+      <c r="AA19" s="81"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="21" t="s">
         <v>20</v>
@@ -4196,28 +4196,28 @@
       <c r="A20" s="18">
         <v>2</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="58"/>
-      <c r="G20" s="57" t="s">
+      <c r="F20" s="81"/>
+      <c r="G20" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="81"/>
       <c r="I20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J20" s="57" t="s">
+      <c r="J20" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K20" s="58"/>
+      <c r="K20" s="81"/>
       <c r="L20" s="20" t="s">
         <v>110</v>
       </c>
@@ -4233,17 +4233,17 @@
       <c r="P20" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="58"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="81"/>
       <c r="U20" s="20"/>
       <c r="V20" s="20"/>
       <c r="W20" s="20"/>
-      <c r="X20" s="57"/>
-      <c r="Y20" s="58"/>
-      <c r="Z20" s="57"/>
-      <c r="AA20" s="58"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="81"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="81"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="21" t="s">
         <v>20</v>
@@ -4252,138 +4252,138 @@
     </row>
     <row r="21" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="60"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="23"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="60"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="86"/>
       <c r="I21" s="24"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="60"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="86"/>
       <c r="L21" s="24"/>
       <c r="M21" s="24"/>
       <c r="N21" s="24"/>
       <c r="O21" s="24"/>
       <c r="P21" s="24"/>
-      <c r="Q21" s="61"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="60"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="86"/>
+      <c r="S21" s="85"/>
+      <c r="T21" s="86"/>
       <c r="U21" s="24"/>
       <c r="V21" s="24"/>
       <c r="W21" s="24"/>
-      <c r="X21" s="61"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="61"/>
-      <c r="AA21" s="60"/>
+      <c r="X21" s="85"/>
+      <c r="Y21" s="86"/>
+      <c r="Z21" s="85"/>
+      <c r="AA21" s="86"/>
       <c r="AB21" s="24"/>
       <c r="AC21" s="25"/>
       <c r="AD21" s="11"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="67" t="s">
+      <c r="B22" s="88"/>
+      <c r="C22" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="69" t="s">
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="L22" s="72"/>
-      <c r="M22" s="70" t="s">
+      <c r="L22" s="88"/>
+      <c r="M22" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="N22" s="75"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="69" t="s">
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="75"/>
-      <c r="S22" s="75"/>
-      <c r="T22" s="75"/>
-      <c r="U22" s="72"/>
-      <c r="V22" s="67" t="s">
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="90"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="W22" s="75"/>
-      <c r="X22" s="75"/>
-      <c r="Y22" s="75"/>
-      <c r="Z22" s="75"/>
-      <c r="AA22" s="75"/>
-      <c r="AB22" s="75"/>
-      <c r="AC22" s="78"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="90"/>
+      <c r="Y22" s="90"/>
+      <c r="Z22" s="90"/>
+      <c r="AA22" s="90"/>
+      <c r="AB22" s="90"/>
+      <c r="AC22" s="92"/>
       <c r="AD22" s="11"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A23" s="73"/>
-      <c r="B23" s="74"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="77"/>
-      <c r="P23" s="74"/>
-      <c r="Q23" s="76"/>
-      <c r="R23" s="77"/>
-      <c r="S23" s="77"/>
-      <c r="T23" s="77"/>
-      <c r="U23" s="74"/>
-      <c r="V23" s="76"/>
-      <c r="W23" s="77"/>
-      <c r="X23" s="77"/>
-      <c r="Y23" s="77"/>
-      <c r="Z23" s="77"/>
-      <c r="AA23" s="77"/>
-      <c r="AB23" s="77"/>
-      <c r="AC23" s="79"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="64"/>
+      <c r="T23" s="64"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="91"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="64"/>
+      <c r="AB23" s="64"/>
+      <c r="AC23" s="93"/>
       <c r="AD23" s="11"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="81"/>
       <c r="D24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="64" t="s">
+      <c r="E24" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="58"/>
-      <c r="G24" s="64" t="s">
+      <c r="F24" s="81"/>
+      <c r="G24" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="58"/>
+      <c r="H24" s="81"/>
       <c r="I24" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="64" t="s">
+      <c r="J24" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="58"/>
+      <c r="K24" s="81"/>
       <c r="L24" s="16">
         <v>1</v>
       </c>
@@ -4399,14 +4399,14 @@
       <c r="P24" s="16">
         <v>5</v>
       </c>
-      <c r="Q24" s="63">
+      <c r="Q24" s="80">
         <v>6</v>
       </c>
-      <c r="R24" s="58"/>
-      <c r="S24" s="63">
+      <c r="R24" s="81"/>
+      <c r="S24" s="80">
         <v>7</v>
       </c>
-      <c r="T24" s="58"/>
+      <c r="T24" s="81"/>
       <c r="U24" s="16">
         <v>8</v>
       </c>
@@ -4416,14 +4416,14 @@
       <c r="W24" s="16">
         <v>10</v>
       </c>
-      <c r="X24" s="63">
+      <c r="X24" s="80">
         <v>11</v>
       </c>
-      <c r="Y24" s="58"/>
-      <c r="Z24" s="63">
+      <c r="Y24" s="81"/>
+      <c r="Z24" s="80">
         <v>12</v>
       </c>
-      <c r="AA24" s="58"/>
+      <c r="AA24" s="81"/>
       <c r="AB24" s="16">
         <v>13</v>
       </c>
@@ -4436,28 +4436,28 @@
       <c r="A25" s="18">
         <v>1</v>
       </c>
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="58"/>
+      <c r="C25" s="81"/>
       <c r="D25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="58"/>
-      <c r="G25" s="57" t="s">
+      <c r="F25" s="81"/>
+      <c r="G25" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H25" s="58"/>
+      <c r="H25" s="81"/>
       <c r="I25" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="57" t="s">
+      <c r="J25" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K25" s="58"/>
+      <c r="K25" s="81"/>
       <c r="L25" s="20" t="s">
         <v>103</v>
       </c>
@@ -4473,17 +4473,17 @@
       <c r="P25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="58"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="81"/>
+      <c r="S25" s="83"/>
+      <c r="T25" s="81"/>
       <c r="U25" s="20"/>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="57"/>
-      <c r="Y25" s="58"/>
-      <c r="Z25" s="57"/>
-      <c r="AA25" s="58"/>
+      <c r="X25" s="83"/>
+      <c r="Y25" s="81"/>
+      <c r="Z25" s="83"/>
+      <c r="AA25" s="81"/>
       <c r="AB25" s="20"/>
       <c r="AC25" s="21" t="s">
         <v>20</v>
@@ -4494,28 +4494,28 @@
       <c r="A26" s="18">
         <v>2</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="81"/>
       <c r="D26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="58"/>
-      <c r="G26" s="57" t="s">
+      <c r="F26" s="81"/>
+      <c r="G26" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="H26" s="58"/>
+      <c r="H26" s="81"/>
       <c r="I26" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="57" t="s">
+      <c r="J26" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K26" s="58"/>
+      <c r="K26" s="81"/>
       <c r="L26" s="20" t="s">
         <v>110</v>
       </c>
@@ -4531,17 +4531,17 @@
       <c r="P26" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="58"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="81"/>
+      <c r="S26" s="83"/>
+      <c r="T26" s="81"/>
       <c r="U26" s="20"/>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="57"/>
-      <c r="Y26" s="58"/>
-      <c r="Z26" s="57"/>
-      <c r="AA26" s="58"/>
+      <c r="X26" s="83"/>
+      <c r="Y26" s="81"/>
+      <c r="Z26" s="83"/>
+      <c r="AA26" s="81"/>
       <c r="AB26" s="20"/>
       <c r="AC26" s="21" t="s">
         <v>20</v>
@@ -4550,138 +4550,138 @@
     </row>
     <row r="27" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="22"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="60"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="86"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="60"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="86"/>
       <c r="I27" s="24"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="60"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="86"/>
       <c r="L27" s="24"/>
       <c r="M27" s="24"/>
       <c r="N27" s="24"/>
       <c r="O27" s="24"/>
       <c r="P27" s="24"/>
-      <c r="Q27" s="61"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="61"/>
-      <c r="T27" s="60"/>
+      <c r="Q27" s="85"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="85"/>
+      <c r="T27" s="86"/>
       <c r="U27" s="24"/>
       <c r="V27" s="24"/>
       <c r="W27" s="24"/>
-      <c r="X27" s="61"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="61"/>
-      <c r="AA27" s="60"/>
+      <c r="X27" s="85"/>
+      <c r="Y27" s="86"/>
+      <c r="Z27" s="85"/>
+      <c r="AA27" s="86"/>
       <c r="AB27" s="24"/>
       <c r="AC27" s="25"/>
       <c r="AD27" s="11"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A28" s="65" t="s">
+      <c r="A28" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="67" t="s">
+      <c r="B28" s="88"/>
+      <c r="C28" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="69" t="s">
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="L28" s="72"/>
-      <c r="M28" s="70" t="s">
+      <c r="L28" s="88"/>
+      <c r="M28" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="N28" s="75"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="69" t="s">
+      <c r="N28" s="90"/>
+      <c r="O28" s="90"/>
+      <c r="P28" s="88"/>
+      <c r="Q28" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
-      <c r="U28" s="72"/>
-      <c r="V28" s="67" t="s">
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="88"/>
+      <c r="V28" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="W28" s="75"/>
-      <c r="X28" s="75"/>
-      <c r="Y28" s="75"/>
-      <c r="Z28" s="75"/>
-      <c r="AA28" s="75"/>
-      <c r="AB28" s="75"/>
-      <c r="AC28" s="78"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="90"/>
+      <c r="Z28" s="90"/>
+      <c r="AA28" s="90"/>
+      <c r="AB28" s="90"/>
+      <c r="AC28" s="92"/>
       <c r="AD28" s="11"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A29" s="73"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="76"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="77"/>
-      <c r="P29" s="74"/>
-      <c r="Q29" s="76"/>
-      <c r="R29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="74"/>
-      <c r="V29" s="76"/>
-      <c r="W29" s="77"/>
-      <c r="X29" s="77"/>
-      <c r="Y29" s="77"/>
-      <c r="Z29" s="77"/>
-      <c r="AA29" s="77"/>
-      <c r="AB29" s="77"/>
-      <c r="AC29" s="79"/>
+      <c r="A29" s="89"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="91"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="91"/>
+      <c r="R29" s="64"/>
+      <c r="S29" s="64"/>
+      <c r="T29" s="64"/>
+      <c r="U29" s="65"/>
+      <c r="V29" s="91"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="64"/>
+      <c r="AB29" s="64"/>
+      <c r="AC29" s="93"/>
       <c r="AD29" s="11"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="64" t="s">
+      <c r="B30" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="58"/>
+      <c r="C30" s="81"/>
       <c r="D30" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="64" t="s">
+      <c r="E30" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="58"/>
-      <c r="G30" s="64" t="s">
+      <c r="F30" s="81"/>
+      <c r="G30" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="58"/>
+      <c r="H30" s="81"/>
       <c r="I30" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="64" t="s">
+      <c r="J30" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="K30" s="58"/>
+      <c r="K30" s="81"/>
       <c r="L30" s="16">
         <v>1</v>
       </c>
@@ -4697,14 +4697,14 @@
       <c r="P30" s="16">
         <v>5</v>
       </c>
-      <c r="Q30" s="63">
+      <c r="Q30" s="80">
         <v>6</v>
       </c>
-      <c r="R30" s="58"/>
-      <c r="S30" s="63">
+      <c r="R30" s="81"/>
+      <c r="S30" s="80">
         <v>7</v>
       </c>
-      <c r="T30" s="58"/>
+      <c r="T30" s="81"/>
       <c r="U30" s="16">
         <v>8</v>
       </c>
@@ -4714,14 +4714,14 @@
       <c r="W30" s="16">
         <v>10</v>
       </c>
-      <c r="X30" s="63">
+      <c r="X30" s="80">
         <v>11</v>
       </c>
-      <c r="Y30" s="58"/>
-      <c r="Z30" s="63">
+      <c r="Y30" s="81"/>
+      <c r="Z30" s="80">
         <v>12</v>
       </c>
-      <c r="AA30" s="58"/>
+      <c r="AA30" s="81"/>
       <c r="AB30" s="16">
         <v>13</v>
       </c>
@@ -4734,28 +4734,28 @@
       <c r="A31" s="18">
         <v>1</v>
       </c>
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="58"/>
+      <c r="C31" s="81"/>
       <c r="D31" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="57" t="s">
+      <c r="E31" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="58"/>
-      <c r="G31" s="57" t="s">
+      <c r="F31" s="81"/>
+      <c r="G31" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="58"/>
+      <c r="H31" s="81"/>
       <c r="I31" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J31" s="57" t="s">
+      <c r="J31" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K31" s="58"/>
+      <c r="K31" s="81"/>
       <c r="L31" s="20" t="s">
         <v>100</v>
       </c>
@@ -4771,17 +4771,17 @@
       <c r="P31" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="Q31" s="57"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="57"/>
-      <c r="T31" s="58"/>
+      <c r="Q31" s="83"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="83"/>
+      <c r="T31" s="81"/>
       <c r="U31" s="20"/>
       <c r="V31" s="20"/>
       <c r="W31" s="20"/>
-      <c r="X31" s="57"/>
-      <c r="Y31" s="58"/>
-      <c r="Z31" s="57"/>
-      <c r="AA31" s="58"/>
+      <c r="X31" s="83"/>
+      <c r="Y31" s="81"/>
+      <c r="Z31" s="83"/>
+      <c r="AA31" s="81"/>
       <c r="AB31" s="20"/>
       <c r="AC31" s="21" t="s">
         <v>20</v>
@@ -4792,28 +4792,28 @@
       <c r="A32" s="18">
         <v>2</v>
       </c>
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="58"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="F32" s="58"/>
-      <c r="G32" s="57" t="s">
+      <c r="F32" s="81"/>
+      <c r="G32" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="58"/>
+      <c r="H32" s="81"/>
       <c r="I32" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J32" s="57" t="s">
+      <c r="J32" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K32" s="58"/>
+      <c r="K32" s="81"/>
       <c r="L32" s="20" t="s">
         <v>117</v>
       </c>
@@ -4829,17 +4829,17 @@
       <c r="P32" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Q32" s="57"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="57"/>
-      <c r="T32" s="58"/>
+      <c r="Q32" s="83"/>
+      <c r="R32" s="81"/>
+      <c r="S32" s="83"/>
+      <c r="T32" s="81"/>
       <c r="U32" s="20"/>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="57"/>
-      <c r="Y32" s="58"/>
-      <c r="Z32" s="57"/>
-      <c r="AA32" s="58"/>
+      <c r="X32" s="83"/>
+      <c r="Y32" s="81"/>
+      <c r="Z32" s="83"/>
+      <c r="AA32" s="81"/>
       <c r="AB32" s="20"/>
       <c r="AC32" s="21" t="s">
         <v>20</v>
@@ -4850,28 +4850,28 @@
       <c r="A33" s="18">
         <v>3</v>
       </c>
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="58"/>
+      <c r="C33" s="81"/>
       <c r="D33" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="58"/>
-      <c r="G33" s="57" t="s">
+      <c r="F33" s="81"/>
+      <c r="G33" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="58"/>
+      <c r="H33" s="81"/>
       <c r="I33" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="J33" s="57" t="s">
+      <c r="J33" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K33" s="58"/>
+      <c r="K33" s="81"/>
       <c r="L33" s="20" t="s">
         <v>55</v>
       </c>
@@ -4887,17 +4887,17 @@
       <c r="P33" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="Q33" s="57"/>
-      <c r="R33" s="58"/>
-      <c r="S33" s="57"/>
-      <c r="T33" s="58"/>
+      <c r="Q33" s="83"/>
+      <c r="R33" s="81"/>
+      <c r="S33" s="83"/>
+      <c r="T33" s="81"/>
       <c r="U33" s="20"/>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="57"/>
-      <c r="Y33" s="58"/>
-      <c r="Z33" s="57"/>
-      <c r="AA33" s="58"/>
+      <c r="X33" s="83"/>
+      <c r="Y33" s="81"/>
+      <c r="Z33" s="83"/>
+      <c r="AA33" s="81"/>
       <c r="AB33" s="20"/>
       <c r="AC33" s="21" t="s">
         <v>20</v>
@@ -4908,28 +4908,28 @@
       <c r="A34" s="18">
         <v>4</v>
       </c>
-      <c r="B34" s="62" t="s">
+      <c r="B34" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="58"/>
+      <c r="C34" s="81"/>
       <c r="D34" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="57" t="s">
+      <c r="E34" s="83" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="58"/>
-      <c r="G34" s="57" t="s">
+      <c r="F34" s="81"/>
+      <c r="G34" s="83" t="s">
         <v>121</v>
       </c>
-      <c r="H34" s="58"/>
+      <c r="H34" s="81"/>
       <c r="I34" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="J34" s="57" t="s">
+      <c r="J34" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K34" s="58"/>
+      <c r="K34" s="81"/>
       <c r="L34" s="20" t="s">
         <v>112</v>
       </c>
@@ -4945,17 +4945,17 @@
       <c r="P34" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="Q34" s="57"/>
-      <c r="R34" s="58"/>
-      <c r="S34" s="57"/>
-      <c r="T34" s="58"/>
+      <c r="Q34" s="83"/>
+      <c r="R34" s="81"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="81"/>
       <c r="U34" s="20"/>
       <c r="V34" s="20"/>
       <c r="W34" s="20"/>
-      <c r="X34" s="57"/>
-      <c r="Y34" s="58"/>
-      <c r="Z34" s="57"/>
-      <c r="AA34" s="58"/>
+      <c r="X34" s="83"/>
+      <c r="Y34" s="81"/>
+      <c r="Z34" s="83"/>
+      <c r="AA34" s="81"/>
       <c r="AB34" s="20"/>
       <c r="AC34" s="21" t="s">
         <v>20</v>
@@ -4966,28 +4966,28 @@
       <c r="A35" s="18">
         <v>5</v>
       </c>
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="58"/>
+      <c r="C35" s="81"/>
       <c r="D35" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="F35" s="58"/>
-      <c r="G35" s="57" t="s">
+      <c r="F35" s="81"/>
+      <c r="G35" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="58"/>
+      <c r="H35" s="81"/>
       <c r="I35" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="J35" s="57" t="s">
+      <c r="J35" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="K35" s="58"/>
+      <c r="K35" s="81"/>
       <c r="L35" s="20" t="s">
         <v>29</v>
       </c>
@@ -5003,17 +5003,17 @@
       <c r="P35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="Q35" s="57"/>
-      <c r="R35" s="58"/>
-      <c r="S35" s="57"/>
-      <c r="T35" s="58"/>
+      <c r="Q35" s="83"/>
+      <c r="R35" s="81"/>
+      <c r="S35" s="83"/>
+      <c r="T35" s="81"/>
       <c r="U35" s="20"/>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="57"/>
-      <c r="Y35" s="58"/>
-      <c r="Z35" s="57"/>
-      <c r="AA35" s="58"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="81"/>
+      <c r="Z35" s="83"/>
+      <c r="AA35" s="81"/>
       <c r="AB35" s="20"/>
       <c r="AC35" s="21" t="s">
         <v>20</v>
@@ -5022,106 +5022,106 @@
     </row>
     <row r="36" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
-      <c r="B36" s="59"/>
-      <c r="C36" s="60"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="86"/>
       <c r="D36" s="23"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="60"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="86"/>
       <c r="I36" s="24"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="60"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="86"/>
       <c r="L36" s="24"/>
       <c r="M36" s="24"/>
       <c r="N36" s="24"/>
       <c r="O36" s="24"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="61"/>
-      <c r="R36" s="60"/>
-      <c r="S36" s="61"/>
-      <c r="T36" s="60"/>
+      <c r="Q36" s="85"/>
+      <c r="R36" s="86"/>
+      <c r="S36" s="85"/>
+      <c r="T36" s="86"/>
       <c r="U36" s="24"/>
       <c r="V36" s="24"/>
       <c r="W36" s="24"/>
-      <c r="X36" s="61"/>
-      <c r="Y36" s="60"/>
-      <c r="Z36" s="61"/>
-      <c r="AA36" s="60"/>
+      <c r="X36" s="85"/>
+      <c r="Y36" s="86"/>
+      <c r="Z36" s="85"/>
+      <c r="AA36" s="86"/>
       <c r="AB36" s="24"/>
       <c r="AC36" s="25"/>
       <c r="AD36" s="11"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A37" s="65" t="s">
+      <c r="A37" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="67" t="s">
+      <c r="B37" s="74"/>
+      <c r="C37" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="66"/>
-      <c r="K37" s="69" t="s">
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="L37" s="66"/>
-      <c r="M37" s="70" t="s">
+      <c r="L37" s="74"/>
+      <c r="M37" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="N37" s="68"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="66"/>
-      <c r="Q37" s="69" t="s">
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="74"/>
+      <c r="Q37" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="R37" s="68"/>
-      <c r="S37" s="68"/>
-      <c r="T37" s="68"/>
-      <c r="U37" s="66"/>
-      <c r="V37" s="67" t="s">
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="76"/>
+      <c r="U37" s="74"/>
+      <c r="V37" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="W37" s="68"/>
-      <c r="X37" s="68"/>
-      <c r="Y37" s="68"/>
-      <c r="Z37" s="68"/>
-      <c r="AA37" s="68"/>
-      <c r="AB37" s="68"/>
-      <c r="AC37" s="71"/>
+      <c r="W37" s="76"/>
+      <c r="X37" s="76"/>
+      <c r="Y37" s="76"/>
+      <c r="Z37" s="76"/>
+      <c r="AA37" s="76"/>
+      <c r="AB37" s="76"/>
+      <c r="AC37" s="79"/>
       <c r="AD37" s="11"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="58"/>
+      <c r="C38" s="81"/>
       <c r="D38" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="58"/>
-      <c r="G38" s="64" t="s">
+      <c r="F38" s="81"/>
+      <c r="G38" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="58"/>
+      <c r="H38" s="81"/>
       <c r="I38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="64" t="s">
+      <c r="J38" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="K38" s="58"/>
+      <c r="K38" s="81"/>
       <c r="L38" s="16">
         <v>1</v>
       </c>
@@ -5137,14 +5137,14 @@
       <c r="P38" s="16">
         <v>5</v>
       </c>
-      <c r="Q38" s="63">
+      <c r="Q38" s="80">
         <v>6</v>
       </c>
-      <c r="R38" s="58"/>
-      <c r="S38" s="63">
+      <c r="R38" s="81"/>
+      <c r="S38" s="80">
         <v>7</v>
       </c>
-      <c r="T38" s="58"/>
+      <c r="T38" s="81"/>
       <c r="U38" s="16">
         <v>8</v>
       </c>
@@ -5154,14 +5154,14 @@
       <c r="W38" s="16">
         <v>10</v>
       </c>
-      <c r="X38" s="63">
+      <c r="X38" s="80">
         <v>11</v>
       </c>
-      <c r="Y38" s="58"/>
-      <c r="Z38" s="63">
+      <c r="Y38" s="81"/>
+      <c r="Z38" s="80">
         <v>12</v>
       </c>
-      <c r="AA38" s="58"/>
+      <c r="AA38" s="81"/>
       <c r="AB38" s="16">
         <v>13</v>
       </c>
@@ -5174,28 +5174,28 @@
       <c r="A39" s="18">
         <v>1</v>
       </c>
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="58"/>
+      <c r="C39" s="81"/>
       <c r="D39" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="58"/>
-      <c r="G39" s="57" t="s">
+      <c r="F39" s="81"/>
+      <c r="G39" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="H39" s="58"/>
+      <c r="H39" s="81"/>
       <c r="I39" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J39" s="57" t="s">
+      <c r="J39" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K39" s="58"/>
+      <c r="K39" s="81"/>
       <c r="L39" s="20" t="s">
         <v>117</v>
       </c>
@@ -5211,17 +5211,17 @@
       <c r="P39" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="58"/>
-      <c r="S39" s="57"/>
-      <c r="T39" s="58"/>
+      <c r="Q39" s="83"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="83"/>
+      <c r="T39" s="81"/>
       <c r="U39" s="20"/>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="57"/>
-      <c r="Y39" s="58"/>
-      <c r="Z39" s="57"/>
-      <c r="AA39" s="58"/>
+      <c r="X39" s="83"/>
+      <c r="Y39" s="81"/>
+      <c r="Z39" s="83"/>
+      <c r="AA39" s="81"/>
       <c r="AB39" s="20"/>
       <c r="AC39" s="21" t="s">
         <v>20</v>
@@ -5232,28 +5232,28 @@
       <c r="A40" s="18">
         <v>2</v>
       </c>
-      <c r="B40" s="62" t="s">
+      <c r="B40" s="82" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="58"/>
+      <c r="C40" s="81"/>
       <c r="D40" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="57" t="s">
+      <c r="E40" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="58"/>
-      <c r="G40" s="57" t="s">
+      <c r="F40" s="81"/>
+      <c r="G40" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="H40" s="58"/>
+      <c r="H40" s="81"/>
       <c r="I40" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J40" s="57" t="s">
+      <c r="J40" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K40" s="58"/>
+      <c r="K40" s="81"/>
       <c r="L40" s="20" t="s">
         <v>107</v>
       </c>
@@ -5269,17 +5269,17 @@
       <c r="P40" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="Q40" s="57"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="57"/>
-      <c r="T40" s="58"/>
+      <c r="Q40" s="83"/>
+      <c r="R40" s="81"/>
+      <c r="S40" s="83"/>
+      <c r="T40" s="81"/>
       <c r="U40" s="20"/>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="57"/>
-      <c r="Y40" s="58"/>
-      <c r="Z40" s="57"/>
-      <c r="AA40" s="58"/>
+      <c r="X40" s="83"/>
+      <c r="Y40" s="81"/>
+      <c r="Z40" s="83"/>
+      <c r="AA40" s="81"/>
       <c r="AB40" s="20"/>
       <c r="AC40" s="21" t="s">
         <v>31</v>
@@ -5288,32 +5288,32 @@
     </row>
     <row r="41" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="22"/>
-      <c r="B41" s="59"/>
-      <c r="C41" s="60"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="86"/>
       <c r="D41" s="23"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="60"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="86"/>
       <c r="I41" s="24"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="60"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="86"/>
       <c r="L41" s="24"/>
       <c r="M41" s="24"/>
       <c r="N41" s="24"/>
       <c r="O41" s="24"/>
       <c r="P41" s="24"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="60"/>
-      <c r="S41" s="61"/>
-      <c r="T41" s="60"/>
+      <c r="Q41" s="85"/>
+      <c r="R41" s="86"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="86"/>
       <c r="U41" s="24"/>
       <c r="V41" s="24"/>
       <c r="W41" s="24"/>
-      <c r="X41" s="61"/>
-      <c r="Y41" s="60"/>
-      <c r="Z41" s="61"/>
-      <c r="AA41" s="60"/>
+      <c r="X41" s="85"/>
+      <c r="Y41" s="86"/>
+      <c r="Z41" s="85"/>
+      <c r="AA41" s="86"/>
       <c r="AB41" s="24"/>
       <c r="AC41" s="25"/>
       <c r="AD41" s="11"/>
@@ -5384,92 +5384,138 @@
     </row>
   </sheetData>
   <mergeCells count="240">
-    <mergeCell ref="A1:Q2"/>
-    <mergeCell ref="T2:Z2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="V3:AC3"/>
-    <mergeCell ref="Y4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="Q5:AC5"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:AC6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="U7:AC7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:AC8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:AC9"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:P12"/>
-    <mergeCell ref="Q12:U12"/>
-    <mergeCell ref="V12:AC12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="Z14:AA14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="Z15:AA15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="Q17:U17"/>
-    <mergeCell ref="V17:AC17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="Z18:AA18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="X40:Y40"/>
+    <mergeCell ref="Z40:AA40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="X41:Y41"/>
+    <mergeCell ref="Z41:AA41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="X38:Y38"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="X39:Y39"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:U37"/>
+    <mergeCell ref="V37:AC37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="Z35:AA35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="Z32:AA32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="Z33:AA33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="Z30:AA30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="C28:J29"/>
+    <mergeCell ref="K28:L29"/>
+    <mergeCell ref="M28:P29"/>
+    <mergeCell ref="Q28:U29"/>
+    <mergeCell ref="V28:AC29"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="Z26:AA26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="Z27:AA27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="S24:T24"/>
     <mergeCell ref="A22:B23"/>
     <mergeCell ref="C22:J23"/>
     <mergeCell ref="K22:L23"/>
@@ -5492,138 +5538,92 @@
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="S20:T20"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="Z24:AA24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="A28:B29"/>
-    <mergeCell ref="C28:J29"/>
-    <mergeCell ref="K28:L29"/>
-    <mergeCell ref="M28:P29"/>
-    <mergeCell ref="Q28:U29"/>
-    <mergeCell ref="V28:AC29"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="Z26:AA26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="Z27:AA27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="Z30:AA30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="Z32:AA32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="Z33:AA33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="Z35:AA35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:U37"/>
-    <mergeCell ref="V37:AC37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="X38:Y38"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="X39:Y39"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="X40:Y40"/>
-    <mergeCell ref="Z40:AA40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="X41:Y41"/>
-    <mergeCell ref="Z41:AA41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="Z18:AA18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="Z15:AA15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="Q17:U17"/>
+    <mergeCell ref="V17:AC17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="Z14:AA14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:AC8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:AC9"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:P12"/>
+    <mergeCell ref="Q12:U12"/>
+    <mergeCell ref="V12:AC12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:AC6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="U7:AC7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q5:AC5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="A1:Q2"/>
+    <mergeCell ref="T2:Z2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="V3:AC3"/>
+    <mergeCell ref="Y4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/App_Data/templates/檢驗template.xlsx
+++ b/App_Data/templates/檢驗template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\excelReport\App_Data\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3410DC5C-F253-4512-B2D0-771D80713B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EA85E8-44BE-4A26-A108-AE4514C8971E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{17681C7F-D386-4A82-BD7B-22ABDFEC6765}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17681C7F-D386-4A82-BD7B-22ABDFEC6765}"/>
   </bookViews>
   <sheets>
     <sheet name="templete" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="133">
   <si>
     <t>來源單據</t>
   </si>
@@ -515,12 +515,16 @@
     <t>{{items.vvValue}}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>{{ __end__ }}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -811,6 +815,13 @@
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1783,7 +1794,7 @@
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1875,6 +1886,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2618,308 +2632,335 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="28" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
     </row>
     <row r="2" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="28" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="30" t="s">
+      <c r="J2" s="30"/>
+      <c r="K2" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="29" t="s">
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="29"/>
-      <c r="P2" s="30" t="s">
+      <c r="O2" s="30"/>
+      <c r="P2" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
     </row>
     <row r="3" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="32" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="29" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="29"/>
-      <c r="K3" s="28" t="s">
+      <c r="J3" s="30"/>
+      <c r="K3" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="29" t="s">
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="29"/>
-      <c r="P3" s="28" t="s">
+      <c r="O3" s="30"/>
+      <c r="P3" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="29" t="s">
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="28" t="s">
+      <c r="T3" s="30"/>
+      <c r="U3" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
     </row>
     <row r="4" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="31" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="29" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="29"/>
-      <c r="P4" s="28" t="s">
+      <c r="O4" s="30"/>
+      <c r="P4" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
     </row>
     <row r="5" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
     </row>
     <row r="6" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29" t="s">
+      <c r="D6" s="29"/>
+      <c r="E6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="28" t="s">
+      <c r="F6" s="30"/>
+      <c r="G6" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29" t="s">
+      <c r="H6" s="29"/>
+      <c r="I6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="28" t="s">
+      <c r="J6" s="30"/>
+      <c r="K6" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="29" t="s">
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="37" t="s">
+      <c r="T6" s="30"/>
+      <c r="U6" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
     </row>
     <row r="7" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
     </row>
     <row r="8" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="36"/>
     </row>
     <row r="9" spans="1:24" s="7" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26"/>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-    </row>
-    <row r="10" spans="1:24" s="3" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+    </row>
+    <row r="10" spans="1:24" s="3" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+    </row>
     <row r="11" spans="1:24" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
@@ -3025,7 +3066,7 @@
       <c r="X14" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="C8:X8"/>
     <mergeCell ref="B9:X9"/>
     <mergeCell ref="A5:B5"/>
@@ -3041,18 +3082,12 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:X7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="P3:R3"/>
+    <mergeCell ref="A10:X10"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="Q1:X1"/>
     <mergeCell ref="A2:B2"/>
@@ -3061,6 +3096,13 @@
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:X2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3075,51 +3117,51 @@
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="45" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="47" t="s">
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="44"/>
-      <c r="K1" s="48" t="s">
+      <c r="J1" s="45"/>
+      <c r="K1" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="47" t="s">
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="51"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="40" t="s">
+      <c r="T1" s="52"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="43"/>
     </row>
     <row r="2" spans="1:24" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="54"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="10" t="s">
         <v>23</v>
       </c>
@@ -3132,10 +3174,10 @@
       <c r="G2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="54"/>
+      <c r="I2" s="55"/>
       <c r="J2" s="10">
         <v>1</v>
       </c>
@@ -3175,19 +3217,19 @@
       <c r="V2" s="10">
         <v>13</v>
       </c>
-      <c r="W2" s="54" t="s">
+      <c r="W2" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="X2" s="55"/>
+      <c r="X2" s="56"/>
     </row>
     <row r="3" spans="1:24" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="1" t="s">
         <v>71</v>
       </c>
@@ -3200,10 +3242,10 @@
       <c r="G3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="28"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="8" t="s">
         <v>57</v>
       </c>
@@ -3243,21 +3285,21 @@
       <c r="V3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="W3" s="28" t="s">
+      <c r="W3" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="X3" s="56"/>
+      <c r="X3" s="57"/>
     </row>
     <row r="4" spans="1:24" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -3271,34 +3313,36 @@
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="53"/>
-    </row>
-    <row r="5" spans="1:24" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="54"/>
+    </row>
+    <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
     </row>
     <row r="6" spans="1:24" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -3327,7 +3371,14 @@
       <c r="X6" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="S1:U1"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="W4:X4"/>
@@ -3337,12 +3388,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="W3:X3"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="S1:U1"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3365,25 +3410,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
       <c r="R1" s="11"/>
       <c r="S1" s="11"/>
       <c r="T1" s="11"/>
@@ -3399,317 +3444,317 @@
       <c r="AD1" s="11"/>
     </row>
     <row r="2" spans="1:30" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="58"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
       <c r="AC2" s="11"/>
       <c r="AD2" s="11"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61" t="s">
+      <c r="B3" s="61"/>
+      <c r="C3" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="59" t="s">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="60"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="61"/>
+      <c r="M3" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="59" t="s">
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="62"/>
-      <c r="AB3" s="62"/>
-      <c r="AC3" s="60"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="61"/>
       <c r="AD3" s="11"/>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="61" t="s">
+      <c r="B4" s="66"/>
+      <c r="C4" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="69" t="s">
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="65"/>
-      <c r="M4" s="66" t="s">
+      <c r="L4" s="66"/>
+      <c r="M4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="63" t="s">
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66" t="s">
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="63" t="s">
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
+      <c r="Y4" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="66" t="s">
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="AC4" s="65"/>
+      <c r="AC4" s="66"/>
       <c r="AD4" s="11"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="66" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="63" t="s">
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="64"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="68" t="s">
+      <c r="O5" s="65"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="R5" s="64"/>
-      <c r="S5" s="64"/>
-      <c r="T5" s="64"/>
-      <c r="U5" s="64"/>
-      <c r="V5" s="64"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="64"/>
-      <c r="Z5" s="64"/>
-      <c r="AA5" s="64"/>
-      <c r="AB5" s="64"/>
-      <c r="AC5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="66"/>
       <c r="AD5" s="11"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="68" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="64"/>
-      <c r="U6" s="64"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="64"/>
-      <c r="Y6" s="64"/>
-      <c r="Z6" s="64"/>
-      <c r="AA6" s="64"/>
-      <c r="AB6" s="64"/>
-      <c r="AC6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="66"/>
       <c r="AD6" s="11"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="66" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="63" t="s">
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="65"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="69" t="s">
+      <c r="G7" s="66"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="66" t="s">
+      <c r="L7" s="65"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="O7" s="64"/>
-      <c r="P7" s="65"/>
-      <c r="Q7" s="63" t="s">
+      <c r="O7" s="65"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="65"/>
-      <c r="U7" s="66" t="s">
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="66"/>
+      <c r="U7" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="V7" s="64"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="66"/>
       <c r="AD7" s="11"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="64"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="64"/>
-      <c r="Y8" s="64"/>
-      <c r="Z8" s="64"/>
-      <c r="AA8" s="64"/>
-      <c r="AB8" s="64"/>
-      <c r="AC8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="66"/>
       <c r="AD8" s="11"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="72" t="s">
+      <c r="B9" s="66"/>
+      <c r="C9" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="64"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="64"/>
-      <c r="Q9" s="64"/>
-      <c r="R9" s="64"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="64"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="64"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="64"/>
-      <c r="Y9" s="64"/>
-      <c r="Z9" s="64"/>
-      <c r="AA9" s="64"/>
-      <c r="AB9" s="64"/>
-      <c r="AC9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="65"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="65"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="66"/>
       <c r="AD9" s="11"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
@@ -3777,75 +3822,75 @@
       <c r="AD11" s="11"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="75" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="77" t="s">
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="74"/>
-      <c r="M12" s="78" t="s">
+      <c r="L12" s="75"/>
+      <c r="M12" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="76"/>
-      <c r="O12" s="76"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="77" t="s">
+      <c r="N12" s="77"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="75"/>
+      <c r="Q12" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="76"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="76"/>
-      <c r="U12" s="74"/>
-      <c r="V12" s="75" t="s">
+      <c r="R12" s="77"/>
+      <c r="S12" s="77"/>
+      <c r="T12" s="77"/>
+      <c r="U12" s="75"/>
+      <c r="V12" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="76"/>
-      <c r="X12" s="76"/>
-      <c r="Y12" s="76"/>
-      <c r="Z12" s="76"/>
-      <c r="AA12" s="76"/>
-      <c r="AB12" s="76"/>
-      <c r="AC12" s="79"/>
+      <c r="W12" s="77"/>
+      <c r="X12" s="77"/>
+      <c r="Y12" s="77"/>
+      <c r="Z12" s="77"/>
+      <c r="AA12" s="77"/>
+      <c r="AB12" s="77"/>
+      <c r="AC12" s="80"/>
       <c r="AD12" s="11"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="81"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="84" t="s">
+      <c r="E13" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="81"/>
-      <c r="G13" s="84" t="s">
+      <c r="F13" s="82"/>
+      <c r="G13" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="81"/>
+      <c r="H13" s="82"/>
       <c r="I13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="84" t="s">
+      <c r="J13" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="81"/>
+      <c r="K13" s="82"/>
       <c r="L13" s="16">
         <v>1</v>
       </c>
@@ -3861,14 +3906,14 @@
       <c r="P13" s="16">
         <v>5</v>
       </c>
-      <c r="Q13" s="80">
+      <c r="Q13" s="81">
         <v>6</v>
       </c>
-      <c r="R13" s="81"/>
-      <c r="S13" s="80">
+      <c r="R13" s="82"/>
+      <c r="S13" s="81">
         <v>7</v>
       </c>
-      <c r="T13" s="81"/>
+      <c r="T13" s="82"/>
       <c r="U13" s="16">
         <v>8</v>
       </c>
@@ -3878,14 +3923,14 @@
       <c r="W13" s="16">
         <v>10</v>
       </c>
-      <c r="X13" s="80">
+      <c r="X13" s="81">
         <v>11</v>
       </c>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="80">
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="81">
         <v>12</v>
       </c>
-      <c r="AA13" s="81"/>
+      <c r="AA13" s="82"/>
       <c r="AB13" s="16">
         <v>13</v>
       </c>
@@ -3898,28 +3943,28 @@
       <c r="A14" s="18">
         <v>3</v>
       </c>
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="81"/>
+      <c r="C14" s="82"/>
       <c r="D14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="81"/>
-      <c r="G14" s="83" t="s">
+      <c r="F14" s="82"/>
+      <c r="G14" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="81"/>
+      <c r="H14" s="82"/>
       <c r="I14" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="J14" s="83" t="s">
+      <c r="J14" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="81"/>
+      <c r="K14" s="82"/>
       <c r="L14" s="20" t="s">
         <v>56</v>
       </c>
@@ -3935,17 +3980,17 @@
       <c r="P14" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="81"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="84"/>
+      <c r="T14" s="82"/>
       <c r="U14" s="20"/>
       <c r="V14" s="20"/>
       <c r="W14" s="20"/>
-      <c r="X14" s="83"/>
-      <c r="Y14" s="81"/>
-      <c r="Z14" s="83"/>
-      <c r="AA14" s="81"/>
+      <c r="X14" s="84"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="84"/>
+      <c r="AA14" s="82"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="21" t="s">
         <v>20</v>
@@ -3954,32 +3999,32 @@
     </row>
     <row r="15" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="22"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="86"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="87"/>
       <c r="I15" s="24"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="87"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
-      <c r="Q15" s="85"/>
-      <c r="R15" s="86"/>
-      <c r="S15" s="85"/>
-      <c r="T15" s="86"/>
+      <c r="Q15" s="86"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="86"/>
+      <c r="T15" s="87"/>
       <c r="U15" s="24"/>
       <c r="V15" s="24"/>
       <c r="W15" s="24"/>
-      <c r="X15" s="85"/>
-      <c r="Y15" s="86"/>
-      <c r="Z15" s="85"/>
-      <c r="AA15" s="86"/>
+      <c r="X15" s="86"/>
+      <c r="Y15" s="87"/>
+      <c r="Z15" s="86"/>
+      <c r="AA15" s="87"/>
       <c r="AB15" s="24"/>
       <c r="AC15" s="25"/>
       <c r="AD15" s="11"/>
@@ -4017,75 +4062,75 @@
       <c r="AD16" s="11"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="75" t="s">
+      <c r="B17" s="75"/>
+      <c r="C17" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="77" t="s">
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="74"/>
-      <c r="M17" s="78" t="s">
+      <c r="L17" s="75"/>
+      <c r="M17" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="N17" s="76"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="74"/>
-      <c r="Q17" s="77" t="s">
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="75"/>
+      <c r="Q17" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="R17" s="76"/>
-      <c r="S17" s="76"/>
-      <c r="T17" s="76"/>
-      <c r="U17" s="74"/>
-      <c r="V17" s="75" t="s">
+      <c r="R17" s="77"/>
+      <c r="S17" s="77"/>
+      <c r="T17" s="77"/>
+      <c r="U17" s="75"/>
+      <c r="V17" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="W17" s="76"/>
-      <c r="X17" s="76"/>
-      <c r="Y17" s="76"/>
-      <c r="Z17" s="76"/>
-      <c r="AA17" s="76"/>
-      <c r="AB17" s="76"/>
-      <c r="AC17" s="79"/>
+      <c r="W17" s="77"/>
+      <c r="X17" s="77"/>
+      <c r="Y17" s="77"/>
+      <c r="Z17" s="77"/>
+      <c r="AA17" s="77"/>
+      <c r="AB17" s="77"/>
+      <c r="AC17" s="80"/>
       <c r="AD17" s="11"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="81"/>
+      <c r="C18" s="82"/>
       <c r="D18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="84" t="s">
+      <c r="E18" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="84" t="s">
+      <c r="F18" s="82"/>
+      <c r="G18" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="81"/>
+      <c r="H18" s="82"/>
       <c r="I18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="84" t="s">
+      <c r="J18" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="81"/>
+      <c r="K18" s="82"/>
       <c r="L18" s="16">
         <v>1</v>
       </c>
@@ -4101,14 +4146,14 @@
       <c r="P18" s="16">
         <v>5</v>
       </c>
-      <c r="Q18" s="80">
+      <c r="Q18" s="81">
         <v>6</v>
       </c>
-      <c r="R18" s="81"/>
-      <c r="S18" s="80">
+      <c r="R18" s="82"/>
+      <c r="S18" s="81">
         <v>7</v>
       </c>
-      <c r="T18" s="81"/>
+      <c r="T18" s="82"/>
       <c r="U18" s="16">
         <v>8</v>
       </c>
@@ -4118,14 +4163,14 @@
       <c r="W18" s="16">
         <v>10</v>
       </c>
-      <c r="X18" s="80">
+      <c r="X18" s="81">
         <v>11</v>
       </c>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="80">
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="81">
         <v>12</v>
       </c>
-      <c r="AA18" s="81"/>
+      <c r="AA18" s="82"/>
       <c r="AB18" s="16">
         <v>13</v>
       </c>
@@ -4138,28 +4183,28 @@
       <c r="A19" s="18">
         <v>1</v>
       </c>
-      <c r="B19" s="82" t="s">
+      <c r="B19" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="81"/>
+      <c r="C19" s="82"/>
       <c r="D19" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="81"/>
-      <c r="G19" s="83" t="s">
+      <c r="F19" s="82"/>
+      <c r="G19" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="81"/>
+      <c r="H19" s="82"/>
       <c r="I19" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J19" s="83" t="s">
+      <c r="J19" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K19" s="81"/>
+      <c r="K19" s="82"/>
       <c r="L19" s="20" t="s">
         <v>103</v>
       </c>
@@ -4175,17 +4220,17 @@
       <c r="P19" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="83"/>
-      <c r="T19" s="81"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="82"/>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
-      <c r="X19" s="83"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="83"/>
-      <c r="AA19" s="81"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="82"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="21" t="s">
         <v>20</v>
@@ -4196,28 +4241,28 @@
       <c r="A20" s="18">
         <v>2</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="81"/>
+      <c r="C20" s="82"/>
       <c r="D20" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="81"/>
-      <c r="G20" s="83" t="s">
+      <c r="F20" s="82"/>
+      <c r="G20" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="81"/>
+      <c r="H20" s="82"/>
       <c r="I20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J20" s="83" t="s">
+      <c r="J20" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K20" s="81"/>
+      <c r="K20" s="82"/>
       <c r="L20" s="20" t="s">
         <v>110</v>
       </c>
@@ -4233,17 +4278,17 @@
       <c r="P20" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="81"/>
-      <c r="S20" s="83"/>
-      <c r="T20" s="81"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="84"/>
+      <c r="T20" s="82"/>
       <c r="U20" s="20"/>
       <c r="V20" s="20"/>
       <c r="W20" s="20"/>
-      <c r="X20" s="83"/>
-      <c r="Y20" s="81"/>
-      <c r="Z20" s="83"/>
-      <c r="AA20" s="81"/>
+      <c r="X20" s="84"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="84"/>
+      <c r="AA20" s="82"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="21" t="s">
         <v>20</v>
@@ -4252,138 +4297,138 @@
     </row>
     <row r="21" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
-      <c r="B21" s="87"/>
-      <c r="C21" s="86"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="23"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="87"/>
       <c r="I21" s="24"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="86"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="87"/>
       <c r="L21" s="24"/>
       <c r="M21" s="24"/>
       <c r="N21" s="24"/>
       <c r="O21" s="24"/>
       <c r="P21" s="24"/>
-      <c r="Q21" s="85"/>
-      <c r="R21" s="86"/>
-      <c r="S21" s="85"/>
-      <c r="T21" s="86"/>
+      <c r="Q21" s="86"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="86"/>
+      <c r="T21" s="87"/>
       <c r="U21" s="24"/>
       <c r="V21" s="24"/>
       <c r="W21" s="24"/>
-      <c r="X21" s="85"/>
-      <c r="Y21" s="86"/>
-      <c r="Z21" s="85"/>
-      <c r="AA21" s="86"/>
+      <c r="X21" s="86"/>
+      <c r="Y21" s="87"/>
+      <c r="Z21" s="86"/>
+      <c r="AA21" s="87"/>
       <c r="AB21" s="24"/>
       <c r="AC21" s="25"/>
       <c r="AD21" s="11"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="75" t="s">
+      <c r="B22" s="89"/>
+      <c r="C22" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="77" t="s">
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="L22" s="88"/>
-      <c r="M22" s="78" t="s">
+      <c r="L22" s="89"/>
+      <c r="M22" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="N22" s="90"/>
-      <c r="O22" s="90"/>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="77" t="s">
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="R22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="T22" s="90"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="75" t="s">
+      <c r="R22" s="91"/>
+      <c r="S22" s="91"/>
+      <c r="T22" s="91"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="W22" s="90"/>
-      <c r="X22" s="90"/>
-      <c r="Y22" s="90"/>
-      <c r="Z22" s="90"/>
-      <c r="AA22" s="90"/>
-      <c r="AB22" s="90"/>
-      <c r="AC22" s="92"/>
+      <c r="W22" s="91"/>
+      <c r="X22" s="91"/>
+      <c r="Y22" s="91"/>
+      <c r="Z22" s="91"/>
+      <c r="AA22" s="91"/>
+      <c r="AB22" s="91"/>
+      <c r="AC22" s="93"/>
       <c r="AD22" s="11"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="91"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="64"/>
-      <c r="X23" s="64"/>
-      <c r="Y23" s="64"/>
-      <c r="Z23" s="64"/>
-      <c r="AA23" s="64"/>
-      <c r="AB23" s="64"/>
-      <c r="AC23" s="93"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="92"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="94"/>
       <c r="AD23" s="11"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="81"/>
+      <c r="C24" s="82"/>
       <c r="D24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="84" t="s">
+      <c r="E24" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="81"/>
-      <c r="G24" s="84" t="s">
+      <c r="F24" s="82"/>
+      <c r="G24" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="81"/>
+      <c r="H24" s="82"/>
       <c r="I24" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="84" t="s">
+      <c r="J24" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="81"/>
+      <c r="K24" s="82"/>
       <c r="L24" s="16">
         <v>1</v>
       </c>
@@ -4399,14 +4444,14 @@
       <c r="P24" s="16">
         <v>5</v>
       </c>
-      <c r="Q24" s="80">
+      <c r="Q24" s="81">
         <v>6</v>
       </c>
-      <c r="R24" s="81"/>
-      <c r="S24" s="80">
+      <c r="R24" s="82"/>
+      <c r="S24" s="81">
         <v>7</v>
       </c>
-      <c r="T24" s="81"/>
+      <c r="T24" s="82"/>
       <c r="U24" s="16">
         <v>8</v>
       </c>
@@ -4416,14 +4461,14 @@
       <c r="W24" s="16">
         <v>10</v>
       </c>
-      <c r="X24" s="80">
+      <c r="X24" s="81">
         <v>11</v>
       </c>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="80">
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="81">
         <v>12</v>
       </c>
-      <c r="AA24" s="81"/>
+      <c r="AA24" s="82"/>
       <c r="AB24" s="16">
         <v>13</v>
       </c>
@@ -4436,28 +4481,28 @@
       <c r="A25" s="18">
         <v>1</v>
       </c>
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="81"/>
+      <c r="C25" s="82"/>
       <c r="D25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="83" t="s">
+      <c r="E25" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="81"/>
-      <c r="G25" s="83" t="s">
+      <c r="F25" s="82"/>
+      <c r="G25" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="H25" s="81"/>
+      <c r="H25" s="82"/>
       <c r="I25" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="83" t="s">
+      <c r="J25" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K25" s="81"/>
+      <c r="K25" s="82"/>
       <c r="L25" s="20" t="s">
         <v>103</v>
       </c>
@@ -4473,17 +4518,17 @@
       <c r="P25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="83"/>
-      <c r="T25" s="81"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="84"/>
+      <c r="T25" s="82"/>
       <c r="U25" s="20"/>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
-      <c r="X25" s="83"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="83"/>
-      <c r="AA25" s="81"/>
+      <c r="X25" s="84"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="82"/>
       <c r="AB25" s="20"/>
       <c r="AC25" s="21" t="s">
         <v>20</v>
@@ -4494,28 +4539,28 @@
       <c r="A26" s="18">
         <v>2</v>
       </c>
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="81"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="83" t="s">
+      <c r="E26" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="81"/>
-      <c r="G26" s="83" t="s">
+      <c r="F26" s="82"/>
+      <c r="G26" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="H26" s="81"/>
+      <c r="H26" s="82"/>
       <c r="I26" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="83" t="s">
+      <c r="J26" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K26" s="81"/>
+      <c r="K26" s="82"/>
       <c r="L26" s="20" t="s">
         <v>110</v>
       </c>
@@ -4531,17 +4576,17 @@
       <c r="P26" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="83"/>
-      <c r="T26" s="81"/>
+      <c r="Q26" s="84"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="84"/>
+      <c r="T26" s="82"/>
       <c r="U26" s="20"/>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
-      <c r="X26" s="83"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="83"/>
-      <c r="AA26" s="81"/>
+      <c r="X26" s="84"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="84"/>
+      <c r="AA26" s="82"/>
       <c r="AB26" s="20"/>
       <c r="AC26" s="21" t="s">
         <v>20</v>
@@ -4550,138 +4595,138 @@
     </row>
     <row r="27" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="22"/>
-      <c r="B27" s="87"/>
-      <c r="C27" s="86"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="87"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="87"/>
       <c r="I27" s="24"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="K27" s="87"/>
       <c r="L27" s="24"/>
       <c r="M27" s="24"/>
       <c r="N27" s="24"/>
       <c r="O27" s="24"/>
       <c r="P27" s="24"/>
-      <c r="Q27" s="85"/>
-      <c r="R27" s="86"/>
-      <c r="S27" s="85"/>
-      <c r="T27" s="86"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="87"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="87"/>
       <c r="U27" s="24"/>
       <c r="V27" s="24"/>
       <c r="W27" s="24"/>
-      <c r="X27" s="85"/>
-      <c r="Y27" s="86"/>
-      <c r="Z27" s="85"/>
-      <c r="AA27" s="86"/>
+      <c r="X27" s="86"/>
+      <c r="Y27" s="87"/>
+      <c r="Z27" s="86"/>
+      <c r="AA27" s="87"/>
       <c r="AB27" s="24"/>
       <c r="AC27" s="25"/>
       <c r="AD27" s="11"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A28" s="73" t="s">
+      <c r="A28" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="88"/>
-      <c r="C28" s="75" t="s">
+      <c r="B28" s="89"/>
+      <c r="C28" s="76" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="77" t="s">
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="L28" s="88"/>
-      <c r="M28" s="78" t="s">
+      <c r="L28" s="89"/>
+      <c r="M28" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="N28" s="90"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="88"/>
-      <c r="Q28" s="77" t="s">
+      <c r="N28" s="91"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="89"/>
+      <c r="Q28" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="R28" s="90"/>
-      <c r="S28" s="90"/>
-      <c r="T28" s="90"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="75" t="s">
+      <c r="R28" s="91"/>
+      <c r="S28" s="91"/>
+      <c r="T28" s="91"/>
+      <c r="U28" s="89"/>
+      <c r="V28" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="W28" s="90"/>
-      <c r="X28" s="90"/>
-      <c r="Y28" s="90"/>
-      <c r="Z28" s="90"/>
-      <c r="AA28" s="90"/>
-      <c r="AB28" s="90"/>
-      <c r="AC28" s="92"/>
+      <c r="W28" s="91"/>
+      <c r="X28" s="91"/>
+      <c r="Y28" s="91"/>
+      <c r="Z28" s="91"/>
+      <c r="AA28" s="91"/>
+      <c r="AB28" s="91"/>
+      <c r="AC28" s="93"/>
       <c r="AD28" s="11"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="91"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="91"/>
-      <c r="R29" s="64"/>
-      <c r="S29" s="64"/>
-      <c r="T29" s="64"/>
-      <c r="U29" s="65"/>
-      <c r="V29" s="91"/>
-      <c r="W29" s="64"/>
-      <c r="X29" s="64"/>
-      <c r="Y29" s="64"/>
-      <c r="Z29" s="64"/>
-      <c r="AA29" s="64"/>
-      <c r="AB29" s="64"/>
-      <c r="AC29" s="93"/>
+      <c r="A29" s="90"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="65"/>
+      <c r="U29" s="66"/>
+      <c r="V29" s="92"/>
+      <c r="W29" s="65"/>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="65"/>
+      <c r="Z29" s="65"/>
+      <c r="AA29" s="65"/>
+      <c r="AB29" s="65"/>
+      <c r="AC29" s="94"/>
       <c r="AD29" s="11"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="84" t="s">
+      <c r="B30" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="81"/>
+      <c r="C30" s="82"/>
       <c r="D30" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="84" t="s">
+      <c r="E30" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="81"/>
-      <c r="G30" s="84" t="s">
+      <c r="F30" s="82"/>
+      <c r="G30" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="81"/>
+      <c r="H30" s="82"/>
       <c r="I30" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="84" t="s">
+      <c r="J30" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="K30" s="81"/>
+      <c r="K30" s="82"/>
       <c r="L30" s="16">
         <v>1</v>
       </c>
@@ -4697,14 +4742,14 @@
       <c r="P30" s="16">
         <v>5</v>
       </c>
-      <c r="Q30" s="80">
+      <c r="Q30" s="81">
         <v>6</v>
       </c>
-      <c r="R30" s="81"/>
-      <c r="S30" s="80">
+      <c r="R30" s="82"/>
+      <c r="S30" s="81">
         <v>7</v>
       </c>
-      <c r="T30" s="81"/>
+      <c r="T30" s="82"/>
       <c r="U30" s="16">
         <v>8</v>
       </c>
@@ -4714,14 +4759,14 @@
       <c r="W30" s="16">
         <v>10</v>
       </c>
-      <c r="X30" s="80">
+      <c r="X30" s="81">
         <v>11</v>
       </c>
-      <c r="Y30" s="81"/>
-      <c r="Z30" s="80">
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="81">
         <v>12</v>
       </c>
-      <c r="AA30" s="81"/>
+      <c r="AA30" s="82"/>
       <c r="AB30" s="16">
         <v>13</v>
       </c>
@@ -4734,28 +4779,28 @@
       <c r="A31" s="18">
         <v>1</v>
       </c>
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="81"/>
+      <c r="C31" s="82"/>
       <c r="D31" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="83" t="s">
+      <c r="E31" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="81"/>
-      <c r="G31" s="83" t="s">
+      <c r="F31" s="82"/>
+      <c r="G31" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="81"/>
+      <c r="H31" s="82"/>
       <c r="I31" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J31" s="83" t="s">
+      <c r="J31" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K31" s="81"/>
+      <c r="K31" s="82"/>
       <c r="L31" s="20" t="s">
         <v>100</v>
       </c>
@@ -4771,17 +4816,17 @@
       <c r="P31" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="Q31" s="83"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="83"/>
-      <c r="T31" s="81"/>
+      <c r="Q31" s="84"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="84"/>
+      <c r="T31" s="82"/>
       <c r="U31" s="20"/>
       <c r="V31" s="20"/>
       <c r="W31" s="20"/>
-      <c r="X31" s="83"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="83"/>
-      <c r="AA31" s="81"/>
+      <c r="X31" s="84"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="84"/>
+      <c r="AA31" s="82"/>
       <c r="AB31" s="20"/>
       <c r="AC31" s="21" t="s">
         <v>20</v>
@@ -4792,28 +4837,28 @@
       <c r="A32" s="18">
         <v>2</v>
       </c>
-      <c r="B32" s="82" t="s">
+      <c r="B32" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="81"/>
+      <c r="C32" s="82"/>
       <c r="D32" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="83" t="s">
+      <c r="E32" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="F32" s="81"/>
-      <c r="G32" s="83" t="s">
+      <c r="F32" s="82"/>
+      <c r="G32" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="81"/>
+      <c r="H32" s="82"/>
       <c r="I32" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J32" s="83" t="s">
+      <c r="J32" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K32" s="81"/>
+      <c r="K32" s="82"/>
       <c r="L32" s="20" t="s">
         <v>117</v>
       </c>
@@ -4829,17 +4874,17 @@
       <c r="P32" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Q32" s="83"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="83"/>
-      <c r="T32" s="81"/>
+      <c r="Q32" s="84"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="84"/>
+      <c r="T32" s="82"/>
       <c r="U32" s="20"/>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
-      <c r="X32" s="83"/>
-      <c r="Y32" s="81"/>
-      <c r="Z32" s="83"/>
-      <c r="AA32" s="81"/>
+      <c r="X32" s="84"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="84"/>
+      <c r="AA32" s="82"/>
       <c r="AB32" s="20"/>
       <c r="AC32" s="21" t="s">
         <v>20</v>
@@ -4850,28 +4895,28 @@
       <c r="A33" s="18">
         <v>3</v>
       </c>
-      <c r="B33" s="82" t="s">
+      <c r="B33" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="81"/>
+      <c r="C33" s="82"/>
       <c r="D33" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="83" t="s">
+      <c r="E33" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="83" t="s">
+      <c r="F33" s="82"/>
+      <c r="G33" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="81"/>
+      <c r="H33" s="82"/>
       <c r="I33" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="J33" s="83" t="s">
+      <c r="J33" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K33" s="81"/>
+      <c r="K33" s="82"/>
       <c r="L33" s="20" t="s">
         <v>55</v>
       </c>
@@ -4887,17 +4932,17 @@
       <c r="P33" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="83"/>
-      <c r="T33" s="81"/>
+      <c r="Q33" s="84"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="84"/>
+      <c r="T33" s="82"/>
       <c r="U33" s="20"/>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
-      <c r="X33" s="83"/>
-      <c r="Y33" s="81"/>
-      <c r="Z33" s="83"/>
-      <c r="AA33" s="81"/>
+      <c r="X33" s="84"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="84"/>
+      <c r="AA33" s="82"/>
       <c r="AB33" s="20"/>
       <c r="AC33" s="21" t="s">
         <v>20</v>
@@ -4908,28 +4953,28 @@
       <c r="A34" s="18">
         <v>4</v>
       </c>
-      <c r="B34" s="82" t="s">
+      <c r="B34" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="81"/>
+      <c r="C34" s="82"/>
       <c r="D34" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="83" t="s">
+      <c r="E34" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="81"/>
-      <c r="G34" s="83" t="s">
+      <c r="F34" s="82"/>
+      <c r="G34" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="H34" s="81"/>
+      <c r="H34" s="82"/>
       <c r="I34" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K34" s="81"/>
+      <c r="K34" s="82"/>
       <c r="L34" s="20" t="s">
         <v>112</v>
       </c>
@@ -4945,17 +4990,17 @@
       <c r="P34" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="Q34" s="83"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="83"/>
-      <c r="T34" s="81"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="82"/>
       <c r="U34" s="20"/>
       <c r="V34" s="20"/>
       <c r="W34" s="20"/>
-      <c r="X34" s="83"/>
-      <c r="Y34" s="81"/>
-      <c r="Z34" s="83"/>
-      <c r="AA34" s="81"/>
+      <c r="X34" s="84"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="84"/>
+      <c r="AA34" s="82"/>
       <c r="AB34" s="20"/>
       <c r="AC34" s="21" t="s">
         <v>20</v>
@@ -4966,28 +5011,28 @@
       <c r="A35" s="18">
         <v>5</v>
       </c>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="81"/>
+      <c r="C35" s="82"/>
       <c r="D35" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="83" t="s">
+      <c r="E35" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="F35" s="81"/>
-      <c r="G35" s="83" t="s">
+      <c r="F35" s="82"/>
+      <c r="G35" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="81"/>
+      <c r="H35" s="82"/>
       <c r="I35" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="J35" s="83" t="s">
+      <c r="J35" s="84" t="s">
         <v>126</v>
       </c>
-      <c r="K35" s="81"/>
+      <c r="K35" s="82"/>
       <c r="L35" s="20" t="s">
         <v>29</v>
       </c>
@@ -5003,17 +5048,17 @@
       <c r="P35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="81"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="81"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="82"/>
+      <c r="S35" s="84"/>
+      <c r="T35" s="82"/>
       <c r="U35" s="20"/>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
-      <c r="X35" s="83"/>
-      <c r="Y35" s="81"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="81"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="82"/>
+      <c r="Z35" s="84"/>
+      <c r="AA35" s="82"/>
       <c r="AB35" s="20"/>
       <c r="AC35" s="21" t="s">
         <v>20</v>
@@ -5022,106 +5067,106 @@
     </row>
     <row r="36" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="86"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="23"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="87"/>
       <c r="I36" s="24"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="86"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="87"/>
       <c r="L36" s="24"/>
       <c r="M36" s="24"/>
       <c r="N36" s="24"/>
       <c r="O36" s="24"/>
       <c r="P36" s="24"/>
-      <c r="Q36" s="85"/>
-      <c r="R36" s="86"/>
-      <c r="S36" s="85"/>
-      <c r="T36" s="86"/>
+      <c r="Q36" s="86"/>
+      <c r="R36" s="87"/>
+      <c r="S36" s="86"/>
+      <c r="T36" s="87"/>
       <c r="U36" s="24"/>
       <c r="V36" s="24"/>
       <c r="W36" s="24"/>
-      <c r="X36" s="85"/>
-      <c r="Y36" s="86"/>
-      <c r="Z36" s="85"/>
-      <c r="AA36" s="86"/>
+      <c r="X36" s="86"/>
+      <c r="Y36" s="87"/>
+      <c r="Z36" s="86"/>
+      <c r="AA36" s="87"/>
       <c r="AB36" s="24"/>
       <c r="AC36" s="25"/>
       <c r="AD36" s="11"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="74"/>
-      <c r="C37" s="75" t="s">
+      <c r="B37" s="75"/>
+      <c r="C37" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="74"/>
-      <c r="K37" s="77" t="s">
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="L37" s="74"/>
-      <c r="M37" s="78" t="s">
+      <c r="L37" s="75"/>
+      <c r="M37" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="N37" s="76"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="74"/>
-      <c r="Q37" s="77" t="s">
+      <c r="N37" s="77"/>
+      <c r="O37" s="77"/>
+      <c r="P37" s="75"/>
+      <c r="Q37" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="76"/>
-      <c r="U37" s="74"/>
-      <c r="V37" s="75" t="s">
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="77"/>
+      <c r="U37" s="75"/>
+      <c r="V37" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="W37" s="76"/>
-      <c r="X37" s="76"/>
-      <c r="Y37" s="76"/>
-      <c r="Z37" s="76"/>
-      <c r="AA37" s="76"/>
-      <c r="AB37" s="76"/>
-      <c r="AC37" s="79"/>
+      <c r="W37" s="77"/>
+      <c r="X37" s="77"/>
+      <c r="Y37" s="77"/>
+      <c r="Z37" s="77"/>
+      <c r="AA37" s="77"/>
+      <c r="AB37" s="77"/>
+      <c r="AC37" s="80"/>
       <c r="AD37" s="11"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="84" t="s">
+      <c r="B38" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="81"/>
+      <c r="C38" s="82"/>
       <c r="D38" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="84" t="s">
+      <c r="E38" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="81"/>
-      <c r="G38" s="84" t="s">
+      <c r="F38" s="82"/>
+      <c r="G38" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="81"/>
+      <c r="H38" s="82"/>
       <c r="I38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="84" t="s">
+      <c r="J38" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="K38" s="81"/>
+      <c r="K38" s="82"/>
       <c r="L38" s="16">
         <v>1</v>
       </c>
@@ -5137,14 +5182,14 @@
       <c r="P38" s="16">
         <v>5</v>
       </c>
-      <c r="Q38" s="80">
+      <c r="Q38" s="81">
         <v>6</v>
       </c>
-      <c r="R38" s="81"/>
-      <c r="S38" s="80">
+      <c r="R38" s="82"/>
+      <c r="S38" s="81">
         <v>7</v>
       </c>
-      <c r="T38" s="81"/>
+      <c r="T38" s="82"/>
       <c r="U38" s="16">
         <v>8</v>
       </c>
@@ -5154,14 +5199,14 @@
       <c r="W38" s="16">
         <v>10</v>
       </c>
-      <c r="X38" s="80">
+      <c r="X38" s="81">
         <v>11</v>
       </c>
-      <c r="Y38" s="81"/>
-      <c r="Z38" s="80">
+      <c r="Y38" s="82"/>
+      <c r="Z38" s="81">
         <v>12</v>
       </c>
-      <c r="AA38" s="81"/>
+      <c r="AA38" s="82"/>
       <c r="AB38" s="16">
         <v>13</v>
       </c>
@@ -5174,28 +5219,28 @@
       <c r="A39" s="18">
         <v>1</v>
       </c>
-      <c r="B39" s="82" t="s">
+      <c r="B39" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="81"/>
+      <c r="C39" s="82"/>
       <c r="D39" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E39" s="83" t="s">
+      <c r="E39" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="81"/>
-      <c r="G39" s="83" t="s">
+      <c r="F39" s="82"/>
+      <c r="G39" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="H39" s="81"/>
+      <c r="H39" s="82"/>
       <c r="I39" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J39" s="83" t="s">
+      <c r="J39" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K39" s="81"/>
+      <c r="K39" s="82"/>
       <c r="L39" s="20" t="s">
         <v>117</v>
       </c>
@@ -5211,17 +5256,17 @@
       <c r="P39" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="Q39" s="83"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="83"/>
-      <c r="T39" s="81"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="82"/>
+      <c r="S39" s="84"/>
+      <c r="T39" s="82"/>
       <c r="U39" s="20"/>
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
-      <c r="X39" s="83"/>
-      <c r="Y39" s="81"/>
-      <c r="Z39" s="83"/>
-      <c r="AA39" s="81"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="82"/>
+      <c r="Z39" s="84"/>
+      <c r="AA39" s="82"/>
       <c r="AB39" s="20"/>
       <c r="AC39" s="21" t="s">
         <v>20</v>
@@ -5232,28 +5277,28 @@
       <c r="A40" s="18">
         <v>2</v>
       </c>
-      <c r="B40" s="82" t="s">
+      <c r="B40" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="81"/>
+      <c r="C40" s="82"/>
       <c r="D40" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="83" t="s">
+      <c r="E40" s="84" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="81"/>
-      <c r="G40" s="83" t="s">
+      <c r="F40" s="82"/>
+      <c r="G40" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="H40" s="81"/>
+      <c r="H40" s="82"/>
       <c r="I40" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J40" s="83" t="s">
+      <c r="J40" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="K40" s="81"/>
+      <c r="K40" s="82"/>
       <c r="L40" s="20" t="s">
         <v>107</v>
       </c>
@@ -5269,17 +5314,17 @@
       <c r="P40" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="Q40" s="83"/>
-      <c r="R40" s="81"/>
-      <c r="S40" s="83"/>
-      <c r="T40" s="81"/>
+      <c r="Q40" s="84"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="82"/>
       <c r="U40" s="20"/>
       <c r="V40" s="20"/>
       <c r="W40" s="20"/>
-      <c r="X40" s="83"/>
-      <c r="Y40" s="81"/>
-      <c r="Z40" s="83"/>
-      <c r="AA40" s="81"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="82"/>
+      <c r="Z40" s="84"/>
+      <c r="AA40" s="82"/>
       <c r="AB40" s="20"/>
       <c r="AC40" s="21" t="s">
         <v>31</v>
@@ -5288,32 +5333,32 @@
     </row>
     <row r="41" spans="1:30" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="22"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="86"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="87"/>
       <c r="D41" s="23"/>
-      <c r="E41" s="85"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="87"/>
       <c r="I41" s="24"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
       <c r="L41" s="24"/>
       <c r="M41" s="24"/>
       <c r="N41" s="24"/>
       <c r="O41" s="24"/>
       <c r="P41" s="24"/>
-      <c r="Q41" s="85"/>
-      <c r="R41" s="86"/>
-      <c r="S41" s="85"/>
-      <c r="T41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="86"/>
+      <c r="T41" s="87"/>
       <c r="U41" s="24"/>
       <c r="V41" s="24"/>
       <c r="W41" s="24"/>
-      <c r="X41" s="85"/>
-      <c r="Y41" s="86"/>
-      <c r="Z41" s="85"/>
-      <c r="AA41" s="86"/>
+      <c r="X41" s="86"/>
+      <c r="Y41" s="87"/>
+      <c r="Z41" s="86"/>
+      <c r="AA41" s="87"/>
       <c r="AB41" s="24"/>
       <c r="AC41" s="25"/>
       <c r="AD41" s="11"/>
